--- a/rawdata.xlsx
+++ b/rawdata.xlsx
@@ -5,18 +5,20 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\u_backup\行为实验-终点冥想\Mindfulness\Data and Code V3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\u_backup\行为实验-终点冥想\Mindfulness\Data and Code V5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6426780-4E57-4B4C-A905-4E2F27408D2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92D2B7D2-CA4E-4072-9A5B-1447C4F5496C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="rawdata1" sheetId="1" r:id="rId1"/>
+    <sheet name="rawdata2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">rawdata1!$A$1:$R$149</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">rawdata2!$A$1:$H$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="718" uniqueCount="193">
   <si>
     <t>SubjNum</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -191,6 +193,466 @@
   </si>
   <si>
     <t>Account_Immediate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mental image</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>生机盎然的大自然中，郁郁葱葱生命力非常旺盛</t>
+  </si>
+  <si>
+    <t>我想像的是自己一个人面对死亡的时候，我的家人朋友都在我的身边，我特别难过，感觉自己在和一切告别。</t>
+  </si>
+  <si>
+    <t>眼前出现了一片大草地。草地上撒落着许多不知名的野花,点缀在绿茵茵的草地间,显得十分五彩缤纷</t>
+  </si>
+  <si>
+    <t>寂静、空洞、黑暗</t>
+  </si>
+  <si>
+    <t>繁星，优美</t>
+  </si>
+  <si>
+    <t>我冥想的场景是我在即将死亡前，我一个人孤零零的，即使亲戚朋友都在我的身边，我也会觉得特别的害怕。</t>
+  </si>
+  <si>
+    <t>自己走在一座桥上，周围是铅色的简笔画背景，随着指导语依次出现我的家人、朋友，以及过去的事情再放送</t>
+  </si>
+  <si>
+    <t>我要死了，然后我面前有一堆钱，然后世界被坏人统治了等等等</t>
+  </si>
+  <si>
+    <t>躺在一片绿地上，身边山清水秀，家人朋友就在旁边，其乐融融</t>
+  </si>
+  <si>
+    <t>站在夜晚的星空里，眺望着人间，感受这灯火，但是人生早晚归于灰尘，一切都不值得</t>
+  </si>
+  <si>
+    <t>本来是第三人称视角看到“我”走在路上，觉得不合适，调整成了第一人称视角。我走在类似隧道一样的地上，但很快周围出现了建筑物，是黑夜，所以建筑有光亮。</t>
+  </si>
+  <si>
+    <t>旁边春暖花开 有枝蔓 但是往前被光遮住看不清前方有什么 感觉未知而不可预测</t>
+  </si>
+  <si>
+    <t>过去已经过去，未来还未到来，就只剩下此时此刻</t>
+  </si>
+  <si>
+    <t>写作业，期中考；草坪，阳光，鸟叫，圣光；躺在床上，周围围着一圈的人，我的家人和挚友；</t>
+  </si>
+  <si>
+    <t>大海、蓝天、白云</t>
+  </si>
+  <si>
+    <t>空旷的大堂我漂浮在半空，目睹着躺在棺椁里的自己，和围绕在身边的亲朋。自己是那么虚无缥缈。</t>
+  </si>
+  <si>
+    <t>冥想事感觉紧张身体不适，想到过去，时间，爸爸，妈妈，老公，女儿</t>
+  </si>
+  <si>
+    <t>周围很黑，面前有一团白色的光。</t>
+  </si>
+  <si>
+    <t>珍惜现在，享受生活</t>
+  </si>
+  <si>
+    <t>感觉自己处在一个无人的幽静的小村落，过着与世无争的生活</t>
+  </si>
+  <si>
+    <t>草地、树林，清新的空气，大自然的味道。</t>
+  </si>
+  <si>
+    <t>一片黑暗，寂静</t>
+  </si>
+  <si>
+    <t>我联想到了宇宙，联想到了生活的点点滴滴，此时此刻我只想冷静的看待这个世界发生的一切。</t>
+  </si>
+  <si>
+    <t>想起一些爱的人，想到一些错过的事情</t>
+  </si>
+  <si>
+    <t>坐在很暗的屋子里，前面只有一扇窗，窗外有一些亮光</t>
+  </si>
+  <si>
+    <t>闭上眼睛脑海会出现很多的情景，心情，高兴，痛快，悲伤</t>
+  </si>
+  <si>
+    <t>柳树下的我 小桥流水 微风拂面</t>
+  </si>
+  <si>
+    <t>在夜晚自己的卧室里点上蜡烛和香薰</t>
+  </si>
+  <si>
+    <t>我看到了我爱的人和爱我的人，我想起了如果我死了，他们会多么难过，所以我会好好的活着，幸福地活着。</t>
+  </si>
+  <si>
+    <t>想到了自己平凡的一天</t>
+  </si>
+  <si>
+    <t>在家里，天气很温暖，太阳很舒服，和家人朋友待在一起开开玩笑，吃吃饭，聊聊天</t>
+  </si>
+  <si>
+    <t>一条时空隧道，隧道里贴着记录我从小到大成长的照片，隧道的尽头是一片花海，很温暖很明亮</t>
+  </si>
+  <si>
+    <t>阳光 鲜花 白色窗帘 大床 朋友 音乐 花香 鸟叫</t>
+  </si>
+  <si>
+    <t>一条昏暗的灰色的路，看不到尽头</t>
+  </si>
+  <si>
+    <t>我处在一片温暖的光亮之中，很静谧</t>
+  </si>
+  <si>
+    <t>温暖的阳光，家人朋友的微笑</t>
+  </si>
+  <si>
+    <t>回想起在球场上拼搏的样子</t>
+  </si>
+  <si>
+    <t>阳光，朋友，大床，白窗帘，花瓣</t>
+  </si>
+  <si>
+    <t>到最后一年祥和，感觉特别的轻松，这世界就我一人，我就是整个世界</t>
+  </si>
+  <si>
+    <t>一步步走向终点，不断努力，不断进步，人生很长又不长，终点就是彼岸。</t>
+  </si>
+  <si>
+    <t>温暖、光亮；我独自走在一条路上，一步一步向前；我在一个空间打坐，悬浮，头上是我关心的事物比如学习、爱好等，周围是我关心的人，它们都围着我环绕</t>
+  </si>
+  <si>
+    <t>躺在空无一人的大草原上</t>
+  </si>
+  <si>
+    <t>白色 温暖</t>
+  </si>
+  <si>
+    <t>生活很平静，四处风景优美</t>
+  </si>
+  <si>
+    <t>白 干净</t>
+  </si>
+  <si>
+    <t>没有喧嚣没有噪杂</t>
+  </si>
+  <si>
+    <t>想到了与家人朋友们在一起的场景</t>
+  </si>
+  <si>
+    <t>一家人在春节晚上团聚在一起，暖黄的灯光，爱人，温柔对我说话</t>
+  </si>
+  <si>
+    <t>小山丘上，走在独木桥上，一直向前走</t>
+  </si>
+  <si>
+    <t>森林花园 隧道 不知所措</t>
+  </si>
+  <si>
+    <t>身边没有人，一片空灵，感觉精神很放松</t>
+  </si>
+  <si>
+    <t>安然散步，即将离世</t>
+  </si>
+  <si>
+    <t>现在是温暖和明亮的，似乎一切都是美好的</t>
+  </si>
+  <si>
+    <t>一间禅室，燃着清香，空气清新，无人打扰。</t>
+  </si>
+  <si>
+    <t>温馨的场景，欢乐的时光</t>
+  </si>
+  <si>
+    <t>想到自己的一生，想到一些难忘的事</t>
+  </si>
+  <si>
+    <t>想象和我爷爷奶奶一起的场景</t>
+  </si>
+  <si>
+    <t>一片空白，身临其境，心情非常忐忑</t>
+  </si>
+  <si>
+    <t>舒服</t>
+  </si>
+  <si>
+    <t>大海中飘浮</t>
+  </si>
+  <si>
+    <t>我在小树林里，周围静静的，阳光透着树叶照在我脸上，舒服惬意</t>
+  </si>
+  <si>
+    <t>说实话一片黑，但音频中提到“生命的通道”等的时候确实也有想过是怎么样一条路</t>
+  </si>
+  <si>
+    <t>脑海中的画面就是清晨早上第一缕阳光洒下，仰头向上，眼光洒在脸上，舒服放松</t>
+  </si>
+  <si>
+    <t>一个人站在悬崖边上 感受这死亡带来的恐惧感 一跃就是万丈深渊</t>
+  </si>
+  <si>
+    <t>一个人站在长长的、金黄的、光线强烈的时光隧道；（想象中）低头看所处的位置时四周又完全黑暗，底下是万丈深渊</t>
+  </si>
+  <si>
+    <t>来到了茫茫宇宙</t>
+  </si>
+  <si>
+    <t>我在一片漆黑中一条有星光的隧道里</t>
+  </si>
+  <si>
+    <t>海滩上行走，临终死去</t>
+  </si>
+  <si>
+    <t>就像进入巨大的空旷的空间里，远处有光，一步一步走向光</t>
+  </si>
+  <si>
+    <t>静静的躺在床上，弥留之际意识还清醒，一生就像过电影</t>
+  </si>
+  <si>
+    <t>沙漠，蓝天，花香，安静</t>
+  </si>
+  <si>
+    <t>从一片黑暗到鸟语花香到家人环绕</t>
+  </si>
+  <si>
+    <t>感觉自己一个人呆在一个空无一人、安静的地方</t>
+  </si>
+  <si>
+    <t>阿甘正传中，阿甘妈妈去世前躺的那张床，我希望它更窄一点，这样去世前家人可以站的离我近一点</t>
+  </si>
+  <si>
+    <t>我冥想到我走在生命最后一刻的路上，那是一条发光的像银河一样的彩带，我四处张望，不时回头，慢慢的向远处飘去，尽头是一个光亮的圆圈，看不到里面是什么，当我走到尽头时，我停下了，除了光亮的彩带，到处是漆黑的，我顿住了。</t>
+  </si>
+  <si>
+    <t>光亮的整体式暖色调场景，内心悲伤但是主体放松</t>
+  </si>
+  <si>
+    <t>白色的隧道在黑色的空间里 隧道墙上有黑白的相片 古朴典雅的相片 然后在草地上 有湖有树有鸟 有一些朋友在一起</t>
+  </si>
+  <si>
+    <t>就是一个明亮且平静的道路上走着。</t>
+  </si>
+  <si>
+    <t>我一直在向前走，渐渐走到了光明处</t>
+  </si>
+  <si>
+    <t>一条有些昏暗的道路，尽头是一口水井，砖石砌成的墙壁上有几盏灯</t>
+  </si>
+  <si>
+    <t>一个人，在空旷的水面有一艘小船，黑暗的，</t>
+  </si>
+  <si>
+    <t>一片黑暗，没有尽头</t>
+  </si>
+  <si>
+    <t>仿佛漫步在沙滩上，沿着水沙交接处慢慢走</t>
+  </si>
+  <si>
+    <t>自己什么都抛掉，跟着视频所说的每一个场景感同身受，身临其境，被催眠的感觉</t>
+  </si>
+  <si>
+    <t>冥想的是此刻的生活，充满了阳光，在新的一年里春暖花开，大地回暖，生活是那么的充实且有意义。</t>
+  </si>
+  <si>
+    <t>联想到《星际穿越》里的虫洞隧道，然后想到《心灵奇旅》那条狭长的单行道，重点时候的风景有四季和景点变换</t>
+  </si>
+  <si>
+    <t>充实忙碌的工作和学习，海边悠闲地散步，温馨的房子</t>
+  </si>
+  <si>
+    <t>氛围感强的昏黑的餐厅</t>
+  </si>
+  <si>
+    <t>我坐在一块石头上，很平静，吸气，呼气。</t>
+  </si>
+  <si>
+    <t>在一个黑暗的空间尽头，有一处充满光明，充满鸟语花香的人间仙境。</t>
+  </si>
+  <si>
+    <t>我感觉自己好像身处水中，周围的噪音我也听不见了，世界好像只有我自己一人，没有什么事情是大不了的，当下很重要。我感觉自己很像一只在水中遨游的鱼，无拘无束</t>
+  </si>
+  <si>
+    <t>周围什么都没有，只有像黄昏时的光，光汇聚之处，是结束，也是新生。</t>
+  </si>
+  <si>
+    <t>周围是宇宙，走在像管道或者水族馆底部一样的通道里，很长</t>
+  </si>
+  <si>
+    <t>我想象到一个很亮很暖和的干净车站。</t>
+  </si>
+  <si>
+    <t>一个人走在一条很长的没有尽头的路上，周围没有什么空间限制，面前有一扇关上的门，门里面是有光亮的，打开门的门后是黑暗的没有光的</t>
+  </si>
+  <si>
+    <t>阳光 花园 鸟鸣</t>
+  </si>
+  <si>
+    <t>慢慢放松自己，想现在的生活，想家人一起出去游玩，欢乐的事情</t>
+  </si>
+  <si>
+    <t>漫漫的长路，一个人在孤独的前行着，一路风景各异。</t>
+  </si>
+  <si>
+    <t>放松心情，吸气呼气。我们走到了人生的路口，这个路口就是此刻，我们活在此时、活在此刻</t>
+  </si>
+  <si>
+    <t>一个人走在路的尽头，前面是一片白芒的虚无。回忆一生，忍不住的流泪。最后一个人走向未知的前路中。</t>
+  </si>
+  <si>
+    <t>不知道</t>
+  </si>
+  <si>
+    <t>我看上去像个橡胶小人，走到白色的架空平台上，有个门，门前就我一个，一直在想每时每刻世界上有那么多人去世为什么门前都没什么人</t>
+  </si>
+  <si>
+    <t>金色的麦田，乡村小路</t>
+  </si>
+  <si>
+    <t>我感到自己正在经历死亡</t>
+  </si>
+  <si>
+    <t>房间、书柜、狗、扶手椅、雨、暖光灯</t>
+  </si>
+  <si>
+    <t>脑海里想自己进入了一个无底空旷的黑洞。</t>
+  </si>
+  <si>
+    <t>父母等家人，我走在通向光明的隧道上，学习任务</t>
+  </si>
+  <si>
+    <t>脑海有一扇半开的门，门缝透过微微一束光。</t>
+  </si>
+  <si>
+    <t>一团雾，很空</t>
+  </si>
+  <si>
+    <t>想象的场景是洒满阳光的病房，亲友在病房外等候，想要的事物都已经得到，我抬眼看着窗外的大树，静静离世。</t>
+  </si>
+  <si>
+    <t>一个人，平静的看着夜空，深邃而安静</t>
+  </si>
+  <si>
+    <t>和家人一起生活、一起出去游玩景点的开心心情、一起打闹的场景，在公司努力工作被表扬的场景，还有生病去医院的自暴自弃的情感，还有陪伴着孩子一起长大的开心日子，还有生活中遇到的心酸往事</t>
+  </si>
+  <si>
+    <t>身处一片光亮之中，走在一条路上</t>
+  </si>
+  <si>
+    <t>在死亡的边缘，回看自己过去的一生</t>
+  </si>
+  <si>
+    <t>一个空旷透明的列车站台，铁轨两侧是生机盎然的山</t>
+  </si>
+  <si>
+    <t>病房、蓝白病号服、药水、挂瓶</t>
+  </si>
+  <si>
+    <t>安静的房间，窗外透进来的光，窗帘下摆飘动，车流声在很远很远处传来</t>
+  </si>
+  <si>
+    <t>医院的病房内，白发苍苍的老人，周围是跪在地上或站在老人身边握着老人手的年轻人，除老人外所有人都在哭</t>
+  </si>
+  <si>
+    <t>我在一个时光通道里，我在现在，一步步向前走，未来也一步步靠近</t>
+  </si>
+  <si>
+    <t>感到自己好像在海边，自己仿佛将要乘上一艘小船漂浮在一望无际的大海上</t>
+  </si>
+  <si>
+    <t>一片花海，温暖，明亮，鸟叫清脆，花香迷人</t>
+  </si>
+  <si>
+    <t>就仿佛是回想自己的一生，从童年到长大成人，每一个精彩的，难过的，记忆瞬间都如幻灯片般飞速过去。</t>
+  </si>
+  <si>
+    <t>在黑色的走廊里走路 停在门前</t>
+  </si>
+  <si>
+    <t>走在路上，路标是自己的年龄，尽头是万丈光芒，终点有一个长桌</t>
+  </si>
+  <si>
+    <t>一个黑暗阴冷的小角落，像一个墙角一样</t>
+  </si>
+  <si>
+    <t>临终时的场景是医院的病床上，我的家人朋友都围绕在我的身边，那天是白天，阳光普照，暖意也照在白色的病床上。我安详的走了，他们泣不成声。</t>
+  </si>
+  <si>
+    <t>似乎坐在海边，虽然有浪花，却完全不被打扰。又或者坐在山间，清新的空气，美丽的花朵，一切都是那么的和谐。</t>
+  </si>
+  <si>
+    <t>感觉漂浮在水上</t>
+  </si>
+  <si>
+    <t>阳光沐浴在公园的草地上，有几个小孩在嬉戏。</t>
+  </si>
+  <si>
+    <t>阳光、清晨、春天、小院、花开、温暖</t>
+  </si>
+  <si>
+    <t>回忆高中和准备高考的场景，看到一个在奔跑的自己，和家人一起看电视</t>
+  </si>
+  <si>
+    <t>夜晚 寒冷的冬天 岔路口</t>
+  </si>
+  <si>
+    <t>我在一个类似于隧道的通道里不断向前走着，前方后方都是光亮，我记忆深刻的一些事件漂浮在空中供我观看。</t>
+  </si>
+  <si>
+    <t>前路断绝、悬崖、雪山、风雪、独自一人</t>
+  </si>
+  <si>
+    <t>冥想时，忽明忽暗，想到了我的家人、朋友，也想到了我已经死去的祖辈，想活在当下。</t>
+  </si>
+  <si>
+    <t>幽深的隧道 身体无法动弹 大脑无法思考</t>
+  </si>
+  <si>
+    <t>空白为主，会穿插一些阳光、草地的画面</t>
+  </si>
+  <si>
+    <t>自己一个人慢慢走向终点，平静的周围，豪华的房子，看着电视，安详的度过最后的时间</t>
+  </si>
+  <si>
+    <t>周末和朋友去周末游的场景</t>
+  </si>
+  <si>
+    <t>海边，微风，孤岛</t>
+  </si>
+  <si>
+    <t>空虚 困惑 过去缓慢展开 疑惑 后悔</t>
+  </si>
+  <si>
+    <t>感觉自己马上就要飞走了</t>
+  </si>
+  <si>
+    <t>野外草地废弃铁路旁的长椅（是我很久以前的一个梦里的场景）</t>
+  </si>
+  <si>
+    <t>站在人生隧道的尽头，后面是一望无尽的黑暗</t>
+  </si>
+  <si>
+    <t>树林中太阳升起</t>
+  </si>
+  <si>
+    <t>海底的沙漠</t>
+  </si>
+  <si>
+    <t>四处都是漆黑一片，沿着一条小河流，虽然水量不多，但还是可以听到流水的声音，温度有点冷，但抬头还是可以看到微光</t>
+  </si>
+  <si>
+    <t>我行走在一条隧道里，四周像电影放映一般闪现着我生命中出现的人，他们来了，他们又走了，最终只有我自己，前面不远处有一个极光亮的出口，我慢慢地向出口走去......</t>
+  </si>
+  <si>
+    <t>SelfRelatedness</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SocialCloseness</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EmotionalValence</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -256,7 +718,37 @@
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="6">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -8010,15 +8502,3924 @@
   <autoFilter ref="A1:R149" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C2:C12">
-    <cfRule type="cellIs" dxfId="2" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="5" priority="6" operator="greaterThan">
       <formula>2000</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="7" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="4" priority="7" operator="greaterThan">
       <formula>2000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D2:D149">
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="greaterThan">
+      <formula>2000</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A83961B-D3AA-4A11-B288-3206DF149635}">
+  <dimension ref="A1:H149"/>
+  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="12.796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.53125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.1328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.06640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="143.796875" customWidth="1"/>
+    <col min="6" max="6" width="21.19921875" customWidth="1"/>
+    <col min="7" max="7" width="18.265625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1">
+        <v>2</v>
+      </c>
+      <c r="D2" s="1">
+        <v>29</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F2">
+        <v>8</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1">
+        <v>2</v>
+      </c>
+      <c r="D3" s="1">
+        <v>29</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F3">
+        <v>3</v>
+      </c>
+      <c r="G3">
+        <v>8</v>
+      </c>
+      <c r="H3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1">
+        <v>2</v>
+      </c>
+      <c r="D4" s="1">
+        <v>24</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F4">
+        <v>8</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" s="1">
+        <v>1</v>
+      </c>
+      <c r="D5" s="1">
+        <v>28</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="1">
+        <v>1</v>
+      </c>
+      <c r="D6" s="1">
+        <v>22</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F6">
+        <v>8</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="1">
+        <v>1</v>
+      </c>
+      <c r="D7" s="1">
+        <v>32</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>8</v>
+      </c>
+      <c r="H7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C8" s="1">
+        <v>2</v>
+      </c>
+      <c r="D8" s="1">
+        <v>21</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F8">
+        <v>5</v>
+      </c>
+      <c r="G8">
+        <v>8</v>
+      </c>
+      <c r="H8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" s="1">
+        <v>1</v>
+      </c>
+      <c r="D9" s="1">
+        <v>29</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F9">
+        <v>3</v>
+      </c>
+      <c r="G9">
+        <v>8</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C10" s="1">
+        <v>2</v>
+      </c>
+      <c r="D10" s="1">
+        <v>27</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F10">
+        <v>10</v>
+      </c>
+      <c r="G10">
+        <v>3</v>
+      </c>
+      <c r="H10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C11" s="1">
+        <v>2</v>
+      </c>
+      <c r="D11" s="1">
+        <v>32</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F11">
+        <v>3</v>
+      </c>
+      <c r="G11">
+        <v>8</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C12" s="1">
+        <v>1</v>
+      </c>
+      <c r="D12" s="1">
+        <v>29</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F12">
+        <v>5</v>
+      </c>
+      <c r="G12">
+        <v>3</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="1">
+        <v>2</v>
+      </c>
+      <c r="D13" s="1">
+        <v>23</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F13">
+        <v>5</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>1</v>
+      </c>
+      <c r="C14" s="1">
+        <v>2</v>
+      </c>
+      <c r="D14" s="1">
+        <v>21</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F14">
+        <v>5</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>38</v>
+      </c>
+      <c r="C15" s="1">
+        <v>2</v>
+      </c>
+      <c r="D15" s="1">
+        <v>22</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F15">
+        <v>8</v>
+      </c>
+      <c r="G15">
+        <v>5</v>
+      </c>
+      <c r="H15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="1">
+        <v>1</v>
+      </c>
+      <c r="D16" s="1">
+        <v>25</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F16">
+        <v>8</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" s="1">
+        <v>2</v>
+      </c>
+      <c r="D17" s="1">
+        <v>29</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F17">
+        <v>3</v>
+      </c>
+      <c r="G17">
+        <v>10</v>
+      </c>
+      <c r="H17">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C18" s="1">
+        <v>2</v>
+      </c>
+      <c r="D18" s="1">
+        <v>22</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F18">
+        <v>3</v>
+      </c>
+      <c r="G18">
+        <v>8</v>
+      </c>
+      <c r="H18">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>1</v>
+      </c>
+      <c r="C19" s="1">
+        <v>2</v>
+      </c>
+      <c r="D19" s="1">
+        <v>20</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F19">
+        <v>5</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20" s="1">
+        <v>1</v>
+      </c>
+      <c r="D20" s="1">
+        <v>30</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F20">
+        <v>8</v>
+      </c>
+      <c r="G20">
+        <v>8</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>1</v>
+      </c>
+      <c r="C21" s="1">
+        <v>1</v>
+      </c>
+      <c r="D21" s="1">
+        <v>19</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F21">
+        <v>8</v>
+      </c>
+      <c r="G21">
+        <v>8</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>38</v>
+      </c>
+      <c r="C22" s="1">
+        <v>1</v>
+      </c>
+      <c r="D22" s="1">
+        <v>21</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F22">
+        <v>8</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>38</v>
+      </c>
+      <c r="C23" s="1">
+        <v>2</v>
+      </c>
+      <c r="D23" s="1">
+        <v>24</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F23">
+        <v>3</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>1</v>
+      </c>
+      <c r="C24" s="1">
+        <v>2</v>
+      </c>
+      <c r="D24" s="1">
+        <v>20</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F24">
+        <v>5</v>
+      </c>
+      <c r="G24">
+        <v>8</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>1</v>
+      </c>
+      <c r="C25" s="1">
+        <v>2</v>
+      </c>
+      <c r="D25" s="1">
+        <v>20</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F25">
+        <v>5</v>
+      </c>
+      <c r="G25">
+        <v>8</v>
+      </c>
+      <c r="H25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>38</v>
+      </c>
+      <c r="C26" s="1">
+        <v>2</v>
+      </c>
+      <c r="D26" s="1">
+        <v>19</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F26">
+        <v>5</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>1</v>
+      </c>
+      <c r="C27" s="1">
+        <v>1</v>
+      </c>
+      <c r="D27" s="1">
+        <v>41</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F27">
+        <v>5</v>
+      </c>
+      <c r="G27">
+        <v>8</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>38</v>
+      </c>
+      <c r="C28" s="1">
+        <v>2</v>
+      </c>
+      <c r="D28" s="1">
+        <v>30</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F28">
+        <v>8</v>
+      </c>
+      <c r="G28">
+        <v>8</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>38</v>
+      </c>
+      <c r="C29" s="1">
+        <v>1</v>
+      </c>
+      <c r="D29" s="1">
+        <v>39</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F29">
+        <v>8</v>
+      </c>
+      <c r="G29">
+        <v>8</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>38</v>
+      </c>
+      <c r="C30" s="1">
+        <v>2</v>
+      </c>
+      <c r="D30" s="1">
+        <v>20</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F30">
+        <v>8</v>
+      </c>
+      <c r="G30">
+        <v>10</v>
+      </c>
+      <c r="H30">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>38</v>
+      </c>
+      <c r="C31" s="1">
+        <v>1</v>
+      </c>
+      <c r="D31" s="1">
+        <v>33</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F31">
+        <v>5</v>
+      </c>
+      <c r="G31">
+        <v>8</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>1</v>
+      </c>
+      <c r="C32" s="1">
+        <v>2</v>
+      </c>
+      <c r="D32" s="1">
+        <v>53</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F32">
+        <v>8</v>
+      </c>
+      <c r="G32">
+        <v>3</v>
+      </c>
+      <c r="H32">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C33" s="1">
+        <v>1</v>
+      </c>
+      <c r="D33" s="1">
+        <v>30</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F33">
+        <v>8</v>
+      </c>
+      <c r="G33">
+        <v>8</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>38</v>
+      </c>
+      <c r="C34" s="1">
+        <v>2</v>
+      </c>
+      <c r="D34" s="1">
+        <v>27</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F34">
+        <v>8</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>1</v>
+      </c>
+      <c r="C35" s="1">
+        <v>2</v>
+      </c>
+      <c r="D35" s="1">
+        <v>33</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F35">
+        <v>3</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
+        <v>1</v>
+      </c>
+      <c r="C36" s="1">
+        <v>2</v>
+      </c>
+      <c r="D36" s="1">
+        <v>20</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F36">
+        <v>8</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s">
+        <v>1</v>
+      </c>
+      <c r="C37" s="1">
+        <v>1</v>
+      </c>
+      <c r="D37" s="1">
+        <v>19</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F37">
+        <v>10</v>
+      </c>
+      <c r="G37">
+        <v>3</v>
+      </c>
+      <c r="H37">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
+        <v>1</v>
+      </c>
+      <c r="C38" s="1">
+        <v>2</v>
+      </c>
+      <c r="D38" s="1">
+        <v>19</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F38">
+        <v>5</v>
+      </c>
+      <c r="G38">
+        <v>8</v>
+      </c>
+      <c r="H38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" t="s">
+        <v>1</v>
+      </c>
+      <c r="C39" s="1">
+        <v>2</v>
+      </c>
+      <c r="D39" s="1">
+        <v>19</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F39">
+        <v>8</v>
+      </c>
+      <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" t="s">
+        <v>38</v>
+      </c>
+      <c r="C40" s="1">
+        <v>2</v>
+      </c>
+      <c r="D40" s="1">
+        <v>58</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F40">
+        <v>8</v>
+      </c>
+      <c r="G40">
+        <v>10</v>
+      </c>
+      <c r="H40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" t="s">
+        <v>1</v>
+      </c>
+      <c r="C41" s="1">
+        <v>2</v>
+      </c>
+      <c r="D41" s="1">
+        <v>34</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F41">
+        <v>8</v>
+      </c>
+      <c r="G41">
+        <v>8</v>
+      </c>
+      <c r="H41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C42" s="1">
+        <v>2</v>
+      </c>
+      <c r="D42" s="1">
+        <v>20</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F42">
+        <v>8</v>
+      </c>
+      <c r="G42">
+        <v>8</v>
+      </c>
+      <c r="H42">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" t="s">
+        <v>38</v>
+      </c>
+      <c r="C43" s="1">
+        <v>2</v>
+      </c>
+      <c r="D43" s="1">
+        <v>20</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F43">
+        <v>5</v>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" t="s">
+        <v>1</v>
+      </c>
+      <c r="C44" s="1">
+        <v>2</v>
+      </c>
+      <c r="D44" s="1">
+        <v>19</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F44">
+        <v>8</v>
+      </c>
+      <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" t="s">
+        <v>38</v>
+      </c>
+      <c r="C45" s="1">
+        <v>2</v>
+      </c>
+      <c r="D45" s="1">
+        <v>19</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="F45">
+        <v>8</v>
+      </c>
+      <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" t="s">
+        <v>38</v>
+      </c>
+      <c r="C46" s="1">
+        <v>1</v>
+      </c>
+      <c r="D46" s="1">
+        <v>31</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="F46">
+        <v>5</v>
+      </c>
+      <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47" t="s">
+        <v>1</v>
+      </c>
+      <c r="C47" s="1">
+        <v>2</v>
+      </c>
+      <c r="D47" s="1">
+        <v>26</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F47">
+        <v>5</v>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48" t="s">
+        <v>38</v>
+      </c>
+      <c r="C48" s="1">
+        <v>2</v>
+      </c>
+      <c r="D48" s="1">
+        <v>48</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F48">
+        <v>8</v>
+      </c>
+      <c r="G48">
+        <v>3</v>
+      </c>
+      <c r="H48">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49" t="s">
+        <v>38</v>
+      </c>
+      <c r="C49" s="1">
+        <v>2</v>
+      </c>
+      <c r="D49" s="1">
+        <v>29</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="F49">
+        <v>8</v>
+      </c>
+      <c r="G49">
+        <v>5</v>
+      </c>
+      <c r="H49">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C50" s="1">
+        <v>1</v>
+      </c>
+      <c r="D50" s="1">
+        <v>36</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="F50">
+        <v>5</v>
+      </c>
+      <c r="G50">
+        <v>0</v>
+      </c>
+      <c r="H50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51" t="s">
+        <v>38</v>
+      </c>
+      <c r="C51" s="1">
+        <v>2</v>
+      </c>
+      <c r="D51" s="1">
+        <v>31</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F51">
+        <v>3</v>
+      </c>
+      <c r="G51">
+        <v>0</v>
+      </c>
+      <c r="H51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52" t="s">
+        <v>1</v>
+      </c>
+      <c r="C52" s="1">
+        <v>2</v>
+      </c>
+      <c r="D52" s="1">
+        <v>38</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F52">
+        <v>8</v>
+      </c>
+      <c r="G52">
+        <v>8</v>
+      </c>
+      <c r="H52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53" t="s">
+        <v>38</v>
+      </c>
+      <c r="C53" s="1">
+        <v>1</v>
+      </c>
+      <c r="D53" s="1">
+        <v>27</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F53">
+        <v>3</v>
+      </c>
+      <c r="G53">
+        <v>10</v>
+      </c>
+      <c r="H53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54" t="s">
+        <v>38</v>
+      </c>
+      <c r="C54" s="1">
+        <v>2</v>
+      </c>
+      <c r="D54" s="1">
+        <v>21</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="F54">
+        <v>10</v>
+      </c>
+      <c r="G54">
+        <v>0</v>
+      </c>
+      <c r="H54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55" t="s">
+        <v>1</v>
+      </c>
+      <c r="C55" s="1">
+        <v>1</v>
+      </c>
+      <c r="D55" s="1">
+        <v>28</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="F55">
+        <v>8</v>
+      </c>
+      <c r="G55">
+        <v>0</v>
+      </c>
+      <c r="H55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56" t="s">
+        <v>1</v>
+      </c>
+      <c r="C56" s="1">
+        <v>1</v>
+      </c>
+      <c r="D56" s="1">
+        <v>65</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="F56">
+        <v>10</v>
+      </c>
+      <c r="G56">
+        <v>0</v>
+      </c>
+      <c r="H56">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57" t="s">
+        <v>38</v>
+      </c>
+      <c r="C57" s="1">
+        <v>2</v>
+      </c>
+      <c r="D57" s="1">
+        <v>31</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="F57">
+        <v>5</v>
+      </c>
+      <c r="G57">
+        <v>10</v>
+      </c>
+      <c r="H57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58" t="s">
+        <v>38</v>
+      </c>
+      <c r="C58" s="1">
+        <v>2</v>
+      </c>
+      <c r="D58" s="1">
+        <v>32</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="F58">
+        <v>5</v>
+      </c>
+      <c r="G58">
+        <v>3</v>
+      </c>
+      <c r="H58">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59" t="s">
+        <v>38</v>
+      </c>
+      <c r="C59" s="1">
+        <v>2</v>
+      </c>
+      <c r="D59" s="1">
+        <v>19</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="F59">
+        <v>3</v>
+      </c>
+      <c r="G59">
+        <v>8</v>
+      </c>
+      <c r="H59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60" t="s">
+        <v>1</v>
+      </c>
+      <c r="C60" s="1">
+        <v>1</v>
+      </c>
+      <c r="D60" s="1">
+        <v>25</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F60">
+        <v>8</v>
+      </c>
+      <c r="G60">
+        <v>0</v>
+      </c>
+      <c r="H60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61" t="s">
+        <v>1</v>
+      </c>
+      <c r="C61" s="1">
+        <v>1</v>
+      </c>
+      <c r="D61" s="1">
+        <v>28</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="F61">
+        <v>5</v>
+      </c>
+      <c r="G61">
+        <v>0</v>
+      </c>
+      <c r="H61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62" t="s">
+        <v>38</v>
+      </c>
+      <c r="C62" s="1">
+        <v>2</v>
+      </c>
+      <c r="D62" s="1">
+        <v>22</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F62">
+        <v>8</v>
+      </c>
+      <c r="G62">
+        <v>8</v>
+      </c>
+      <c r="H62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63" t="s">
+        <v>1</v>
+      </c>
+      <c r="C63" s="1">
+        <v>2</v>
+      </c>
+      <c r="D63" s="1">
+        <v>23</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="F63">
+        <v>5</v>
+      </c>
+      <c r="G63">
+        <v>3</v>
+      </c>
+      <c r="H63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64" t="s">
+        <v>38</v>
+      </c>
+      <c r="C64" s="1">
+        <v>2</v>
+      </c>
+      <c r="D64" s="1">
+        <v>19</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="F64">
+        <v>8</v>
+      </c>
+      <c r="G64">
+        <v>3</v>
+      </c>
+      <c r="H64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65" t="s">
+        <v>1</v>
+      </c>
+      <c r="C65" s="1">
+        <v>1</v>
+      </c>
+      <c r="D65" s="1">
+        <v>25</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="F65">
+        <v>0</v>
+      </c>
+      <c r="G65">
+        <v>8</v>
+      </c>
+      <c r="H65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66" t="s">
+        <v>38</v>
+      </c>
+      <c r="C66" s="1">
+        <v>2</v>
+      </c>
+      <c r="D66" s="1">
+        <v>20</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="F66">
+        <v>3</v>
+      </c>
+      <c r="G66">
+        <v>0</v>
+      </c>
+      <c r="H66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="B67" t="s">
+        <v>1</v>
+      </c>
+      <c r="C67" s="1">
+        <v>2</v>
+      </c>
+      <c r="D67" s="1">
+        <v>21</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F67">
+        <v>5</v>
+      </c>
+      <c r="G67">
+        <v>0</v>
+      </c>
+      <c r="H67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A68">
+        <v>67</v>
+      </c>
+      <c r="B68" t="s">
+        <v>38</v>
+      </c>
+      <c r="C68" s="1">
+        <v>1</v>
+      </c>
+      <c r="D68" s="1">
+        <v>20</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F68">
+        <v>5</v>
+      </c>
+      <c r="G68">
+        <v>0</v>
+      </c>
+      <c r="H68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A69">
+        <v>68</v>
+      </c>
+      <c r="B69" t="s">
+        <v>38</v>
+      </c>
+      <c r="C69" s="1">
+        <v>1</v>
+      </c>
+      <c r="D69" s="1">
+        <v>35</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="F69">
+        <v>3</v>
+      </c>
+      <c r="G69">
+        <v>0</v>
+      </c>
+      <c r="H69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A70">
+        <v>69</v>
+      </c>
+      <c r="B70" t="s">
+        <v>1</v>
+      </c>
+      <c r="C70" s="1">
+        <v>2</v>
+      </c>
+      <c r="D70" s="1">
+        <v>21</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="F70">
+        <v>5</v>
+      </c>
+      <c r="G70">
+        <v>0</v>
+      </c>
+      <c r="H70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A71">
+        <v>70</v>
+      </c>
+      <c r="B71" t="s">
+        <v>1</v>
+      </c>
+      <c r="C71" s="1">
+        <v>2</v>
+      </c>
+      <c r="D71" s="1">
+        <v>37</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="F71">
+        <v>3</v>
+      </c>
+      <c r="G71">
+        <v>10</v>
+      </c>
+      <c r="H71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A72">
+        <v>71</v>
+      </c>
+      <c r="B72" t="s">
+        <v>1</v>
+      </c>
+      <c r="C72" s="1">
+        <v>2</v>
+      </c>
+      <c r="D72" s="1">
+        <v>29</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="F72">
+        <v>8</v>
+      </c>
+      <c r="G72">
+        <v>0</v>
+      </c>
+      <c r="H72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A73">
+        <v>72</v>
+      </c>
+      <c r="B73" t="s">
+        <v>38</v>
+      </c>
+      <c r="C73" s="1">
+        <v>2</v>
+      </c>
+      <c r="D73" s="1">
+        <v>32</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="F73">
+        <v>8</v>
+      </c>
+      <c r="G73">
+        <v>8</v>
+      </c>
+      <c r="H73">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A74">
+        <v>73</v>
+      </c>
+      <c r="B74" t="s">
+        <v>38</v>
+      </c>
+      <c r="C74" s="1">
+        <v>1</v>
+      </c>
+      <c r="D74" s="1">
+        <v>25</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="F74">
+        <v>5</v>
+      </c>
+      <c r="G74">
+        <v>8</v>
+      </c>
+      <c r="H74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A75">
+        <v>74</v>
+      </c>
+      <c r="B75" t="s">
+        <v>38</v>
+      </c>
+      <c r="C75" s="1">
+        <v>1</v>
+      </c>
+      <c r="D75" s="1">
+        <v>32</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F75">
+        <v>3</v>
+      </c>
+      <c r="G75">
+        <v>8</v>
+      </c>
+      <c r="H75">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A76">
+        <v>75</v>
+      </c>
+      <c r="B76" t="s">
+        <v>1</v>
+      </c>
+      <c r="C76" s="1">
+        <v>2</v>
+      </c>
+      <c r="D76" s="1">
+        <v>19</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="F76">
+        <v>5</v>
+      </c>
+      <c r="G76">
+        <v>8</v>
+      </c>
+      <c r="H76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A77">
+        <v>76</v>
+      </c>
+      <c r="B77" t="s">
+        <v>38</v>
+      </c>
+      <c r="C77" s="1">
+        <v>1</v>
+      </c>
+      <c r="D77" s="1">
+        <v>20</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="F77">
+        <v>5</v>
+      </c>
+      <c r="G77">
+        <v>8</v>
+      </c>
+      <c r="H77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A78">
+        <v>77</v>
+      </c>
+      <c r="B78" t="s">
+        <v>1</v>
+      </c>
+      <c r="C78" s="1">
+        <v>2</v>
+      </c>
+      <c r="D78" s="1">
+        <v>19</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F78">
+        <v>8</v>
+      </c>
+      <c r="G78">
+        <v>0</v>
+      </c>
+      <c r="H78">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A79">
+        <v>78</v>
+      </c>
+      <c r="B79" t="s">
+        <v>38</v>
+      </c>
+      <c r="C79" s="1">
+        <v>2</v>
+      </c>
+      <c r="D79" s="1">
+        <v>52</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="F79">
+        <v>8</v>
+      </c>
+      <c r="G79">
+        <v>0</v>
+      </c>
+      <c r="H79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A80">
+        <v>79</v>
+      </c>
+      <c r="B80" t="s">
+        <v>1</v>
+      </c>
+      <c r="C80" s="1">
+        <v>1</v>
+      </c>
+      <c r="D80" s="1">
+        <v>34</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="F80">
+        <v>8</v>
+      </c>
+      <c r="G80">
+        <v>8</v>
+      </c>
+      <c r="H80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A81">
+        <v>80</v>
+      </c>
+      <c r="B81" t="s">
+        <v>38</v>
+      </c>
+      <c r="C81" s="1">
+        <v>2</v>
+      </c>
+      <c r="D81" s="1">
+        <v>19</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="F81">
+        <v>5</v>
+      </c>
+      <c r="G81">
+        <v>0</v>
+      </c>
+      <c r="H81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A82">
+        <v>81</v>
+      </c>
+      <c r="B82" t="s">
+        <v>38</v>
+      </c>
+      <c r="C82" s="1">
+        <v>2</v>
+      </c>
+      <c r="D82" s="1">
+        <v>30</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="F82">
+        <v>3</v>
+      </c>
+      <c r="G82">
+        <v>0</v>
+      </c>
+      <c r="H82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A83">
+        <v>82</v>
+      </c>
+      <c r="B83" t="s">
+        <v>1</v>
+      </c>
+      <c r="C83" s="1">
+        <v>1</v>
+      </c>
+      <c r="D83" s="1">
+        <v>31</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="F83">
+        <v>0</v>
+      </c>
+      <c r="G83">
+        <v>0</v>
+      </c>
+      <c r="H83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A84">
+        <v>83</v>
+      </c>
+      <c r="B84" t="s">
+        <v>38</v>
+      </c>
+      <c r="C84" s="1">
+        <v>1</v>
+      </c>
+      <c r="D84" s="1">
+        <v>34</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="F84">
+        <v>8</v>
+      </c>
+      <c r="G84">
+        <v>0</v>
+      </c>
+      <c r="H84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A85">
+        <v>84</v>
+      </c>
+      <c r="B85" t="s">
+        <v>1</v>
+      </c>
+      <c r="C85" s="1">
+        <v>2</v>
+      </c>
+      <c r="D85" s="1">
+        <v>20</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="F85">
+        <v>5</v>
+      </c>
+      <c r="G85">
+        <v>8</v>
+      </c>
+      <c r="H85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A86">
+        <v>85</v>
+      </c>
+      <c r="B86" t="s">
+        <v>38</v>
+      </c>
+      <c r="C86" s="1">
+        <v>2</v>
+      </c>
+      <c r="D86" s="1">
+        <v>28</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="F86">
+        <v>10</v>
+      </c>
+      <c r="G86">
+        <v>3</v>
+      </c>
+      <c r="H86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A87">
+        <v>86</v>
+      </c>
+      <c r="B87" t="s">
+        <v>1</v>
+      </c>
+      <c r="C87" s="1">
+        <v>2</v>
+      </c>
+      <c r="D87" s="1">
+        <v>22</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="F87">
+        <v>5</v>
+      </c>
+      <c r="G87">
+        <v>0</v>
+      </c>
+      <c r="H87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A88">
+        <v>87</v>
+      </c>
+      <c r="B88" t="s">
+        <v>1</v>
+      </c>
+      <c r="C88" s="1">
+        <v>1</v>
+      </c>
+      <c r="D88" s="1">
+        <v>33</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="F88">
+        <v>8</v>
+      </c>
+      <c r="G88">
+        <v>3</v>
+      </c>
+      <c r="H88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A89">
+        <v>88</v>
+      </c>
+      <c r="B89" t="s">
+        <v>1</v>
+      </c>
+      <c r="C89" s="1">
+        <v>1</v>
+      </c>
+      <c r="D89" s="1">
+        <v>28</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="F89">
+        <v>5</v>
+      </c>
+      <c r="G89">
+        <v>0</v>
+      </c>
+      <c r="H89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A90">
+        <v>89</v>
+      </c>
+      <c r="B90" t="s">
+        <v>1</v>
+      </c>
+      <c r="C90" s="1">
+        <v>2</v>
+      </c>
+      <c r="D90" s="1">
+        <v>21</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="F90">
+        <v>5</v>
+      </c>
+      <c r="G90">
+        <v>8</v>
+      </c>
+      <c r="H90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A91">
+        <v>90</v>
+      </c>
+      <c r="B91" t="s">
+        <v>1</v>
+      </c>
+      <c r="C91" s="1">
+        <v>1</v>
+      </c>
+      <c r="D91" s="1">
+        <v>39</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="F91">
+        <v>10</v>
+      </c>
+      <c r="G91">
+        <v>0</v>
+      </c>
+      <c r="H91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A92">
+        <v>91</v>
+      </c>
+      <c r="B92" t="s">
+        <v>38</v>
+      </c>
+      <c r="C92" s="1">
+        <v>2</v>
+      </c>
+      <c r="D92" s="1">
+        <v>20</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="F92">
+        <v>8</v>
+      </c>
+      <c r="G92">
+        <v>8</v>
+      </c>
+      <c r="H92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A93">
+        <v>92</v>
+      </c>
+      <c r="B93" t="s">
+        <v>1</v>
+      </c>
+      <c r="C93" s="1">
+        <v>1</v>
+      </c>
+      <c r="D93" s="1">
+        <v>24</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="F93">
+        <v>5</v>
+      </c>
+      <c r="G93">
+        <v>0</v>
+      </c>
+      <c r="H93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A94">
+        <v>93</v>
+      </c>
+      <c r="B94" t="s">
+        <v>38</v>
+      </c>
+      <c r="C94" s="1">
+        <v>2</v>
+      </c>
+      <c r="D94" s="1">
+        <v>25</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="F94">
+        <v>5</v>
+      </c>
+      <c r="G94">
+        <v>0</v>
+      </c>
+      <c r="H94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A95">
+        <v>94</v>
+      </c>
+      <c r="B95" t="s">
+        <v>38</v>
+      </c>
+      <c r="C95" s="1">
+        <v>2</v>
+      </c>
+      <c r="D95" s="1">
+        <v>21</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="F95">
+        <v>8</v>
+      </c>
+      <c r="G95">
+        <v>0</v>
+      </c>
+      <c r="H95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A96">
+        <v>95</v>
+      </c>
+      <c r="B96" t="s">
+        <v>1</v>
+      </c>
+      <c r="C96" s="1">
+        <v>2</v>
+      </c>
+      <c r="D96" s="1">
+        <v>46</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="F96">
+        <v>3</v>
+      </c>
+      <c r="G96">
+        <v>0</v>
+      </c>
+      <c r="H96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A97">
+        <v>96</v>
+      </c>
+      <c r="B97" t="s">
+        <v>38</v>
+      </c>
+      <c r="C97" s="1">
+        <v>1</v>
+      </c>
+      <c r="D97" s="1">
+        <v>20</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="F97">
+        <v>8</v>
+      </c>
+      <c r="G97">
+        <v>0</v>
+      </c>
+      <c r="H97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A98">
+        <v>97</v>
+      </c>
+      <c r="B98" t="s">
+        <v>1</v>
+      </c>
+      <c r="C98" s="1">
+        <v>1</v>
+      </c>
+      <c r="D98" s="1">
+        <v>20</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="F98">
+        <v>8</v>
+      </c>
+      <c r="G98">
+        <v>8</v>
+      </c>
+      <c r="H98">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A99">
+        <v>98</v>
+      </c>
+      <c r="B99" t="s">
+        <v>38</v>
+      </c>
+      <c r="C99" s="1">
+        <v>1</v>
+      </c>
+      <c r="D99" s="1">
+        <v>21</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="F99">
+        <v>5</v>
+      </c>
+      <c r="G99">
+        <v>3</v>
+      </c>
+      <c r="H99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A100">
+        <v>99</v>
+      </c>
+      <c r="B100" t="s">
+        <v>1</v>
+      </c>
+      <c r="C100" s="1">
+        <v>1</v>
+      </c>
+      <c r="D100" s="1">
+        <v>28</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="F100">
+        <v>5</v>
+      </c>
+      <c r="G100">
+        <v>10</v>
+      </c>
+      <c r="H100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A101">
+        <v>100</v>
+      </c>
+      <c r="B101" t="s">
+        <v>38</v>
+      </c>
+      <c r="C101" s="1">
+        <v>2</v>
+      </c>
+      <c r="D101" s="1">
+        <v>51</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="F101">
+        <v>3</v>
+      </c>
+      <c r="G101">
+        <v>10</v>
+      </c>
+      <c r="H101">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A102">
+        <v>101</v>
+      </c>
+      <c r="B102" t="s">
+        <v>1</v>
+      </c>
+      <c r="C102" s="1">
+        <v>1</v>
+      </c>
+      <c r="D102" s="1">
+        <v>21</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="F102">
+        <v>5</v>
+      </c>
+      <c r="G102">
+        <v>0</v>
+      </c>
+      <c r="H102">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A103">
+        <v>102</v>
+      </c>
+      <c r="B103" t="s">
+        <v>1</v>
+      </c>
+      <c r="C103" s="1">
+        <v>2</v>
+      </c>
+      <c r="D103" s="1">
+        <v>19</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="F103">
+        <v>3</v>
+      </c>
+      <c r="G103">
+        <v>8</v>
+      </c>
+      <c r="H103">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A104">
+        <v>103</v>
+      </c>
+      <c r="B104" t="s">
+        <v>38</v>
+      </c>
+      <c r="C104" s="1">
+        <v>1</v>
+      </c>
+      <c r="D104" s="1">
+        <v>19</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="F104">
+        <v>8</v>
+      </c>
+      <c r="G104">
+        <v>0</v>
+      </c>
+      <c r="H104">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A105">
+        <v>104</v>
+      </c>
+      <c r="B105" t="s">
+        <v>38</v>
+      </c>
+      <c r="C105" s="1">
+        <v>2</v>
+      </c>
+      <c r="D105" s="1">
+        <v>20</v>
+      </c>
+      <c r="E105" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="F105">
+        <v>0</v>
+      </c>
+      <c r="G105">
+        <v>10</v>
+      </c>
+      <c r="H105">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A106">
+        <v>105</v>
+      </c>
+      <c r="B106" t="s">
+        <v>38</v>
+      </c>
+      <c r="C106" s="1">
+        <v>2</v>
+      </c>
+      <c r="D106" s="1">
+        <v>21</v>
+      </c>
+      <c r="E106" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="F106">
+        <v>5</v>
+      </c>
+      <c r="G106">
+        <v>0</v>
+      </c>
+      <c r="H106">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A107">
+        <v>106</v>
+      </c>
+      <c r="B107" t="s">
+        <v>38</v>
+      </c>
+      <c r="C107" s="1">
+        <v>2</v>
+      </c>
+      <c r="D107" s="1">
+        <v>25</v>
+      </c>
+      <c r="E107" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="F107">
+        <v>0</v>
+      </c>
+      <c r="G107">
+        <v>8</v>
+      </c>
+      <c r="H107">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A108">
+        <v>107</v>
+      </c>
+      <c r="B108" t="s">
+        <v>38</v>
+      </c>
+      <c r="C108" s="1">
+        <v>1</v>
+      </c>
+      <c r="D108" s="1">
+        <v>31</v>
+      </c>
+      <c r="E108" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="F108">
+        <v>8</v>
+      </c>
+      <c r="G108">
+        <v>3</v>
+      </c>
+      <c r="H108">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A109">
+        <v>108</v>
+      </c>
+      <c r="B109" t="s">
+        <v>38</v>
+      </c>
+      <c r="C109" s="1">
+        <v>1</v>
+      </c>
+      <c r="D109" s="1">
+        <v>34</v>
+      </c>
+      <c r="E109" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="F109">
+        <v>5</v>
+      </c>
+      <c r="G109">
+        <v>0</v>
+      </c>
+      <c r="H109">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A110">
+        <v>109</v>
+      </c>
+      <c r="B110" t="s">
+        <v>38</v>
+      </c>
+      <c r="C110" s="1">
+        <v>1</v>
+      </c>
+      <c r="D110" s="1">
+        <v>36</v>
+      </c>
+      <c r="E110" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="F110">
+        <v>5</v>
+      </c>
+      <c r="G110">
+        <v>0</v>
+      </c>
+      <c r="H110">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A111">
+        <v>110</v>
+      </c>
+      <c r="B111" t="s">
+        <v>1</v>
+      </c>
+      <c r="C111" s="1">
+        <v>2</v>
+      </c>
+      <c r="D111" s="1">
+        <v>20</v>
+      </c>
+      <c r="E111" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="F111">
+        <v>5</v>
+      </c>
+      <c r="G111">
+        <v>8</v>
+      </c>
+      <c r="H111">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A112">
+        <v>111</v>
+      </c>
+      <c r="B112" t="s">
+        <v>38</v>
+      </c>
+      <c r="C112" s="1">
+        <v>2</v>
+      </c>
+      <c r="D112" s="1">
+        <v>24</v>
+      </c>
+      <c r="E112" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="F112">
+        <v>5</v>
+      </c>
+      <c r="G112">
+        <v>3</v>
+      </c>
+      <c r="H112">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A113">
+        <v>112</v>
+      </c>
+      <c r="B113" t="s">
+        <v>38</v>
+      </c>
+      <c r="C113" s="1">
+        <v>2</v>
+      </c>
+      <c r="D113" s="1">
+        <v>21</v>
+      </c>
+      <c r="E113" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F113">
+        <v>5</v>
+      </c>
+      <c r="G113">
+        <v>8</v>
+      </c>
+      <c r="H113">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A114">
+        <v>113</v>
+      </c>
+      <c r="B114" t="s">
+        <v>1</v>
+      </c>
+      <c r="C114" s="1">
+        <v>1</v>
+      </c>
+      <c r="D114" s="1">
+        <v>25</v>
+      </c>
+      <c r="E114" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="F114">
+        <v>5</v>
+      </c>
+      <c r="G114">
+        <v>0</v>
+      </c>
+      <c r="H114">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A115">
+        <v>114</v>
+      </c>
+      <c r="B115" t="s">
+        <v>38</v>
+      </c>
+      <c r="C115" s="1">
+        <v>2</v>
+      </c>
+      <c r="D115" s="1">
+        <v>32</v>
+      </c>
+      <c r="E115" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="F115">
+        <v>3</v>
+      </c>
+      <c r="G115">
+        <v>10</v>
+      </c>
+      <c r="H115">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A116">
+        <v>115</v>
+      </c>
+      <c r="B116" t="s">
+        <v>1</v>
+      </c>
+      <c r="C116" s="1">
+        <v>2</v>
+      </c>
+      <c r="D116" s="1">
+        <v>19</v>
+      </c>
+      <c r="E116" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="F116">
+        <v>8</v>
+      </c>
+      <c r="G116">
+        <v>0</v>
+      </c>
+      <c r="H116">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A117">
+        <v>116</v>
+      </c>
+      <c r="B117" t="s">
+        <v>1</v>
+      </c>
+      <c r="C117" s="1">
+        <v>1</v>
+      </c>
+      <c r="D117" s="1">
+        <v>19</v>
+      </c>
+      <c r="E117" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="F117">
+        <v>3</v>
+      </c>
+      <c r="G117">
+        <v>0</v>
+      </c>
+      <c r="H117">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A118">
+        <v>117</v>
+      </c>
+      <c r="B118" t="s">
+        <v>38</v>
+      </c>
+      <c r="C118" s="1">
+        <v>2</v>
+      </c>
+      <c r="D118" s="1">
+        <v>19</v>
+      </c>
+      <c r="E118" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="F118">
+        <v>5</v>
+      </c>
+      <c r="G118">
+        <v>0</v>
+      </c>
+      <c r="H118">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A119">
+        <v>118</v>
+      </c>
+      <c r="B119" t="s">
+        <v>1</v>
+      </c>
+      <c r="C119" s="1">
+        <v>2</v>
+      </c>
+      <c r="D119" s="1">
+        <v>19</v>
+      </c>
+      <c r="E119" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F119">
+        <v>3</v>
+      </c>
+      <c r="G119">
+        <v>0</v>
+      </c>
+      <c r="H119">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A120">
+        <v>119</v>
+      </c>
+      <c r="B120" t="s">
+        <v>38</v>
+      </c>
+      <c r="C120" s="1">
+        <v>2</v>
+      </c>
+      <c r="D120" s="1">
+        <v>34</v>
+      </c>
+      <c r="E120" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="F120">
+        <v>5</v>
+      </c>
+      <c r="G120">
+        <v>8</v>
+      </c>
+      <c r="H120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A121">
+        <v>120</v>
+      </c>
+      <c r="B121" t="s">
+        <v>1</v>
+      </c>
+      <c r="C121" s="1">
+        <v>2</v>
+      </c>
+      <c r="D121" s="1">
+        <v>20</v>
+      </c>
+      <c r="E121" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="F121">
+        <v>5</v>
+      </c>
+      <c r="G121">
+        <v>8</v>
+      </c>
+      <c r="H121">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A122">
+        <v>121</v>
+      </c>
+      <c r="B122" t="s">
+        <v>38</v>
+      </c>
+      <c r="C122" s="1">
+        <v>2</v>
+      </c>
+      <c r="D122" s="1">
+        <v>25</v>
+      </c>
+      <c r="E122" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="F122">
+        <v>10</v>
+      </c>
+      <c r="G122">
+        <v>0</v>
+      </c>
+      <c r="H122">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A123">
+        <v>122</v>
+      </c>
+      <c r="B123" t="s">
+        <v>1</v>
+      </c>
+      <c r="C123" s="1">
+        <v>1</v>
+      </c>
+      <c r="D123" s="1">
+        <v>43</v>
+      </c>
+      <c r="E123" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="F123">
+        <v>5</v>
+      </c>
+      <c r="G123">
+        <v>10</v>
+      </c>
+      <c r="H123">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A124">
+        <v>123</v>
+      </c>
+      <c r="B124" t="s">
+        <v>38</v>
+      </c>
+      <c r="C124" s="1">
+        <v>2</v>
+      </c>
+      <c r="D124" s="1">
+        <v>20</v>
+      </c>
+      <c r="E124" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F124">
+        <v>3</v>
+      </c>
+      <c r="G124">
+        <v>0</v>
+      </c>
+      <c r="H124">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A125">
+        <v>124</v>
+      </c>
+      <c r="B125" t="s">
+        <v>1</v>
+      </c>
+      <c r="C125" s="1">
+        <v>2</v>
+      </c>
+      <c r="D125" s="1">
+        <v>36</v>
+      </c>
+      <c r="E125" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="F125">
+        <v>8</v>
+      </c>
+      <c r="G125">
+        <v>8</v>
+      </c>
+      <c r="H125">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A126">
+        <v>125</v>
+      </c>
+      <c r="B126" t="s">
+        <v>1</v>
+      </c>
+      <c r="C126" s="1">
+        <v>2</v>
+      </c>
+      <c r="D126" s="1">
+        <v>20</v>
+      </c>
+      <c r="E126" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="F126">
+        <v>3</v>
+      </c>
+      <c r="G126">
+        <v>0</v>
+      </c>
+      <c r="H126">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A127">
+        <v>126</v>
+      </c>
+      <c r="B127" t="s">
+        <v>38</v>
+      </c>
+      <c r="C127" s="1">
+        <v>2</v>
+      </c>
+      <c r="D127" s="1">
+        <v>19</v>
+      </c>
+      <c r="E127" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="F127">
+        <v>3</v>
+      </c>
+      <c r="G127">
+        <v>8</v>
+      </c>
+      <c r="H127">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A128">
+        <v>127</v>
+      </c>
+      <c r="B128" t="s">
+        <v>38</v>
+      </c>
+      <c r="C128" s="1">
+        <v>2</v>
+      </c>
+      <c r="D128" s="1">
+        <v>23</v>
+      </c>
+      <c r="E128" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="F128">
+        <v>8</v>
+      </c>
+      <c r="G128">
+        <v>0</v>
+      </c>
+      <c r="H128">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A129">
+        <v>128</v>
+      </c>
+      <c r="B129" t="s">
+        <v>1</v>
+      </c>
+      <c r="C129" s="1">
+        <v>1</v>
+      </c>
+      <c r="D129" s="1">
+        <v>31</v>
+      </c>
+      <c r="E129" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F129">
+        <v>5</v>
+      </c>
+      <c r="G129">
+        <v>8</v>
+      </c>
+      <c r="H129">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A130">
+        <v>129</v>
+      </c>
+      <c r="B130" t="s">
+        <v>38</v>
+      </c>
+      <c r="C130" s="1">
+        <v>2</v>
+      </c>
+      <c r="D130" s="1">
+        <v>19</v>
+      </c>
+      <c r="E130" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F130">
+        <v>8</v>
+      </c>
+      <c r="G130">
+        <v>0</v>
+      </c>
+      <c r="H130">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A131">
+        <v>130</v>
+      </c>
+      <c r="B131" t="s">
+        <v>1</v>
+      </c>
+      <c r="C131" s="1">
+        <v>1</v>
+      </c>
+      <c r="D131" s="1">
+        <v>29</v>
+      </c>
+      <c r="E131" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="F131">
+        <v>8</v>
+      </c>
+      <c r="G131">
+        <v>0</v>
+      </c>
+      <c r="H131">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A132">
+        <v>131</v>
+      </c>
+      <c r="B132" t="s">
+        <v>38</v>
+      </c>
+      <c r="C132" s="1">
+        <v>2</v>
+      </c>
+      <c r="D132" s="1">
+        <v>33</v>
+      </c>
+      <c r="E132" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="F132">
+        <v>5</v>
+      </c>
+      <c r="G132">
+        <v>5</v>
+      </c>
+      <c r="H132">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A133">
+        <v>132</v>
+      </c>
+      <c r="B133" t="s">
+        <v>1</v>
+      </c>
+      <c r="C133" s="1">
+        <v>2</v>
+      </c>
+      <c r="D133" s="1">
+        <v>19</v>
+      </c>
+      <c r="E133" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="F133">
+        <v>3</v>
+      </c>
+      <c r="G133">
+        <v>0</v>
+      </c>
+      <c r="H133">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A134">
+        <v>133</v>
+      </c>
+      <c r="B134" t="s">
+        <v>1</v>
+      </c>
+      <c r="C134" s="1">
+        <v>2</v>
+      </c>
+      <c r="D134" s="1">
+        <v>25</v>
+      </c>
+      <c r="E134" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="F134">
+        <v>5</v>
+      </c>
+      <c r="G134">
+        <v>5</v>
+      </c>
+      <c r="H134">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A135">
+        <v>134</v>
+      </c>
+      <c r="B135" t="s">
+        <v>1</v>
+      </c>
+      <c r="C135" s="1">
+        <v>2</v>
+      </c>
+      <c r="D135" s="1">
+        <v>26</v>
+      </c>
+      <c r="E135" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="F135">
+        <v>3</v>
+      </c>
+      <c r="G135">
+        <v>3</v>
+      </c>
+      <c r="H135">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A136">
+        <v>135</v>
+      </c>
+      <c r="B136" t="s">
+        <v>38</v>
+      </c>
+      <c r="C136" s="1">
+        <v>2</v>
+      </c>
+      <c r="D136" s="1">
+        <v>20</v>
+      </c>
+      <c r="E136" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="F136">
+        <v>5</v>
+      </c>
+      <c r="G136">
+        <v>8</v>
+      </c>
+      <c r="H136">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A137">
+        <v>136</v>
+      </c>
+      <c r="B137" t="s">
+        <v>38</v>
+      </c>
+      <c r="C137" s="1">
+        <v>2</v>
+      </c>
+      <c r="D137" s="1">
+        <v>25</v>
+      </c>
+      <c r="E137" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="F137">
+        <v>0</v>
+      </c>
+      <c r="G137">
+        <v>8</v>
+      </c>
+      <c r="H137">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A138">
+        <v>137</v>
+      </c>
+      <c r="B138" t="s">
+        <v>1</v>
+      </c>
+      <c r="C138" s="1">
+        <v>2</v>
+      </c>
+      <c r="D138" s="1">
+        <v>18</v>
+      </c>
+      <c r="E138" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="F138">
+        <v>5</v>
+      </c>
+      <c r="G138">
+        <v>0</v>
+      </c>
+      <c r="H138">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A139">
+        <v>138</v>
+      </c>
+      <c r="B139" t="s">
+        <v>38</v>
+      </c>
+      <c r="C139" s="1">
+        <v>1</v>
+      </c>
+      <c r="D139" s="1">
+        <v>30</v>
+      </c>
+      <c r="E139" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="F139">
+        <v>5</v>
+      </c>
+      <c r="G139">
+        <v>8</v>
+      </c>
+      <c r="H139">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A140">
+        <v>139</v>
+      </c>
+      <c r="B140" t="s">
+        <v>38</v>
+      </c>
+      <c r="C140" s="1">
+        <v>2</v>
+      </c>
+      <c r="D140" s="1">
+        <v>24</v>
+      </c>
+      <c r="E140" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="F140">
+        <v>8</v>
+      </c>
+      <c r="G140">
+        <v>0</v>
+      </c>
+      <c r="H140">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A141">
+        <v>140</v>
+      </c>
+      <c r="B141" t="s">
+        <v>38</v>
+      </c>
+      <c r="C141" s="1">
+        <v>2</v>
+      </c>
+      <c r="D141" s="1">
+        <v>34</v>
+      </c>
+      <c r="E141" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="F141">
+        <v>5</v>
+      </c>
+      <c r="G141">
+        <v>0</v>
+      </c>
+      <c r="H141">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A142">
+        <v>141</v>
+      </c>
+      <c r="B142" t="s">
+        <v>1</v>
+      </c>
+      <c r="C142" s="1">
+        <v>1</v>
+      </c>
+      <c r="D142" s="1">
+        <v>33</v>
+      </c>
+      <c r="E142" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="F142">
+        <v>3</v>
+      </c>
+      <c r="G142">
+        <v>8</v>
+      </c>
+      <c r="H142">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A143">
+        <v>142</v>
+      </c>
+      <c r="B143" t="s">
+        <v>38</v>
+      </c>
+      <c r="C143" s="1">
+        <v>2</v>
+      </c>
+      <c r="D143" s="1">
+        <v>19</v>
+      </c>
+      <c r="E143" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="F143">
+        <v>8</v>
+      </c>
+      <c r="G143">
+        <v>8</v>
+      </c>
+      <c r="H143">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A144">
+        <v>143</v>
+      </c>
+      <c r="B144" t="s">
+        <v>38</v>
+      </c>
+      <c r="C144" s="1">
+        <v>2</v>
+      </c>
+      <c r="D144" s="1">
+        <v>21</v>
+      </c>
+      <c r="E144" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="F144">
+        <v>5</v>
+      </c>
+      <c r="G144">
+        <v>3</v>
+      </c>
+      <c r="H144">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A145">
+        <v>144</v>
+      </c>
+      <c r="B145" t="s">
+        <v>38</v>
+      </c>
+      <c r="C145" s="1">
+        <v>2</v>
+      </c>
+      <c r="D145" s="1">
+        <v>20</v>
+      </c>
+      <c r="E145" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="F145">
+        <v>3</v>
+      </c>
+      <c r="G145">
+        <v>10</v>
+      </c>
+      <c r="H145">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A146">
+        <v>145</v>
+      </c>
+      <c r="B146" t="s">
+        <v>1</v>
+      </c>
+      <c r="C146" s="1">
+        <v>2</v>
+      </c>
+      <c r="D146" s="1">
+        <v>19</v>
+      </c>
+      <c r="E146" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="F146">
+        <v>8</v>
+      </c>
+      <c r="G146">
+        <v>0</v>
+      </c>
+      <c r="H146">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A147">
+        <v>146</v>
+      </c>
+      <c r="B147" t="s">
+        <v>38</v>
+      </c>
+      <c r="C147" s="1">
+        <v>2</v>
+      </c>
+      <c r="D147" s="1">
+        <v>19</v>
+      </c>
+      <c r="E147" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="F147">
+        <v>5</v>
+      </c>
+      <c r="G147">
+        <v>0</v>
+      </c>
+      <c r="H147">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A148">
+        <v>147</v>
+      </c>
+      <c r="B148" t="s">
+        <v>38</v>
+      </c>
+      <c r="C148" s="1">
+        <v>1</v>
+      </c>
+      <c r="D148" s="1">
+        <v>20</v>
+      </c>
+      <c r="E148" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="F148">
+        <v>5</v>
+      </c>
+      <c r="G148">
+        <v>0</v>
+      </c>
+      <c r="H148">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A149">
+        <v>148</v>
+      </c>
+      <c r="B149" t="s">
+        <v>38</v>
+      </c>
+      <c r="C149" s="1">
+        <v>2</v>
+      </c>
+      <c r="D149" s="1">
+        <v>20</v>
+      </c>
+      <c r="E149" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="F149">
+        <v>5</v>
+      </c>
+      <c r="G149">
+        <v>10</v>
+      </c>
+      <c r="H149">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H1" xr:uid="{7A83961B-D3AA-4A11-B288-3206DF149635}"/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="C2:C12">
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="greaterThan">
+      <formula>2000</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="greaterThan">
+      <formula>2000</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D2:D149">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
       <formula>2000</formula>
     </cfRule>
   </conditionalFormatting>

--- a/rawdata.xlsx
+++ b/rawdata.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\u_backup\行为实验-终点冥想\Mindfulness\Data and Code V5\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\u_backup\行为实验-终点冥想\Mindfulness\Data and Code V6\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92D2B7D2-CA4E-4072-9A5B-1447C4F5496C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9A80A32-D394-419C-B945-BC3D651D455F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="rawdata1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="718" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="718" uniqueCount="192">
   <si>
     <t>SubjNum</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -120,10 +120,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>relaxation, sadness, and peace</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>nervousness</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -144,10 +140,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>sadness with relaxation</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>comfort</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -653,6 +645,10 @@
   </si>
   <si>
     <t>EmotionalValence</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>relaxation with sadness</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1080,7 +1076,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>2</v>
@@ -1104,7 +1100,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="K1" s="2" t="s">
         <v>9</v>
@@ -1279,7 +1275,7 @@
         <v>7</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="R4">
         <v>8</v>
@@ -1290,7 +1286,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C5" s="1">
         <v>1</v>
@@ -1329,7 +1325,7 @@
         <v>8</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="P5" s="3">
         <v>6</v>
@@ -1444,7 +1440,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C8" s="1">
         <v>2</v>
@@ -1585,7 +1581,7 @@
         <v>7</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="P10" s="3">
         <v>6</v>
@@ -1798,7 +1794,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C15" s="1">
         <v>2</v>
@@ -1896,7 +1892,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C17" s="1">
         <v>2</v>
@@ -2050,7 +2046,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C20" s="1">
         <v>1</v>
@@ -2095,7 +2091,7 @@
         <v>6</v>
       </c>
       <c r="Q20" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="R20">
         <v>5</v>
@@ -2139,7 +2135,7 @@
         <v>0.4</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N21">
         <v>7</v>
@@ -2153,7 +2149,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C22" s="1">
         <v>1</v>
@@ -2192,7 +2188,7 @@
         <v>6</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="P22" s="3">
         <v>5</v>
@@ -2204,7 +2200,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C23" s="1">
         <v>2</v>
@@ -2353,7 +2349,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C26" s="1">
         <v>2</v>
@@ -2456,7 +2452,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C28" s="1">
         <v>2</v>
@@ -2507,7 +2503,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C29" s="1">
         <v>1</v>
@@ -2554,7 +2550,7 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C30" s="1">
         <v>2</v>
@@ -2605,7 +2601,7 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C31" s="1">
         <v>1</v>
@@ -2750,7 +2746,7 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C34" s="1">
         <v>2</v>
@@ -2942,7 +2938,7 @@
         <v>0.4</v>
       </c>
       <c r="M37" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N37">
         <v>6</v>
@@ -2989,7 +2985,7 @@
         <v>0</v>
       </c>
       <c r="M38" s="1" t="s">
-        <v>22</v>
+        <v>191</v>
       </c>
       <c r="N38">
         <v>6</v>
@@ -3054,7 +3050,7 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C40" s="1">
         <v>2</v>
@@ -3087,7 +3083,7 @@
         <v>0.4</v>
       </c>
       <c r="M40" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N40">
         <v>7</v>
@@ -3212,7 +3208,7 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C43" s="1">
         <v>2</v>
@@ -3251,7 +3247,7 @@
         <v>4</v>
       </c>
       <c r="O43" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P43" s="3">
         <v>7</v>
@@ -3314,7 +3310,7 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C45" s="1">
         <v>2</v>
@@ -3361,7 +3357,7 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C46" s="1">
         <v>1</v>
@@ -3441,7 +3437,7 @@
         <v>0.1</v>
       </c>
       <c r="M47" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N47">
         <v>7</v>
@@ -3455,7 +3451,7 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C48" s="1">
         <v>2</v>
@@ -3502,7 +3498,7 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C49" s="1">
         <v>2</v>
@@ -3591,7 +3587,7 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C51" s="1">
         <v>2</v>
@@ -3675,7 +3671,7 @@
         <v>0.6</v>
       </c>
       <c r="M52" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="N52">
         <v>7</v>
@@ -3689,7 +3685,7 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C53" s="1">
         <v>1</v>
@@ -3728,7 +3724,7 @@
         <v>6</v>
       </c>
       <c r="O53" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="P53" s="3">
         <v>8</v>
@@ -3740,7 +3736,7 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C54" s="1">
         <v>2</v>
@@ -3889,7 +3885,7 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C57" s="1">
         <v>2</v>
@@ -3922,7 +3918,7 @@
         <v>0.4</v>
       </c>
       <c r="M57" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N57">
         <v>9</v>
@@ -3936,7 +3932,7 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C58" s="1">
         <v>2</v>
@@ -3987,7 +3983,7 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C59" s="1">
         <v>2</v>
@@ -4020,7 +4016,7 @@
         <v>0.2</v>
       </c>
       <c r="M59" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N59">
         <v>6</v>
@@ -4135,7 +4131,7 @@
         <v>6</v>
       </c>
       <c r="Q61" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="R61">
         <v>7</v>
@@ -4146,7 +4142,7 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C62" s="1">
         <v>2</v>
@@ -4244,7 +4240,7 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C64" s="1">
         <v>2</v>
@@ -4342,7 +4338,7 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C66" s="1">
         <v>2</v>
@@ -4440,7 +4436,7 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C68" s="1">
         <v>1</v>
@@ -4479,7 +4475,7 @@
         <v>7</v>
       </c>
       <c r="O68" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="P68" s="3">
         <v>5</v>
@@ -4491,7 +4487,7 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C69" s="1">
         <v>1</v>
@@ -4572,7 +4568,7 @@
         <v>7</v>
       </c>
       <c r="O70" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P70" s="3">
         <v>7</v>
@@ -4687,7 +4683,7 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C73" s="1">
         <v>2</v>
@@ -4738,7 +4734,7 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C74" s="1">
         <v>1</v>
@@ -4789,7 +4785,7 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C75" s="1">
         <v>1</v>
@@ -4891,7 +4887,7 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C77" s="1">
         <v>1</v>
@@ -4966,7 +4962,7 @@
         <v>0.2</v>
       </c>
       <c r="M78" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N78">
         <v>6</v>
@@ -4980,7 +4976,7 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C79" s="1">
         <v>2</v>
@@ -5087,7 +5083,7 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C81" s="1">
         <v>2</v>
@@ -5138,7 +5134,7 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C82" s="1">
         <v>2</v>
@@ -5240,7 +5236,7 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C84" s="1">
         <v>1</v>
@@ -5352,7 +5348,7 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C86" s="1">
         <v>2</v>
@@ -5432,7 +5428,7 @@
         <v>0.3</v>
       </c>
       <c r="M87" s="1" t="s">
-        <v>28</v>
+        <v>191</v>
       </c>
       <c r="N87">
         <v>8</v>
@@ -5637,7 +5633,7 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C92" s="1">
         <v>2</v>
@@ -5739,7 +5735,7 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C94" s="1">
         <v>2</v>
@@ -5786,7 +5782,7 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C95" s="1">
         <v>2</v>
@@ -5888,7 +5884,7 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C97" s="1">
         <v>1</v>
@@ -5986,7 +5982,7 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C99" s="1">
         <v>1</v>
@@ -6066,7 +6062,7 @@
         <v>0.4</v>
       </c>
       <c r="M100" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N100">
         <v>8</v>
@@ -6080,7 +6076,7 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C101" s="1">
         <v>2</v>
@@ -6113,7 +6109,7 @@
         <v>0.4</v>
       </c>
       <c r="M101" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N101">
         <v>6</v>
@@ -6225,7 +6221,7 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C104" s="1">
         <v>1</v>
@@ -6276,7 +6272,7 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C105" s="1">
         <v>2</v>
@@ -6327,7 +6323,7 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C106" s="1">
         <v>2</v>
@@ -6374,7 +6370,7 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C107" s="1">
         <v>2</v>
@@ -6421,7 +6417,7 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C108" s="1">
         <v>1</v>
@@ -6472,7 +6468,7 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C109" s="1">
         <v>1</v>
@@ -6519,7 +6515,7 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C110" s="1">
         <v>1</v>
@@ -6564,7 +6560,7 @@
         <v>7</v>
       </c>
       <c r="Q110" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="R110">
         <v>6</v>
@@ -6626,7 +6622,7 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C112" s="1">
         <v>2</v>
@@ -6673,7 +6669,7 @@
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C113" s="1">
         <v>2</v>
@@ -6771,7 +6767,7 @@
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C115" s="1">
         <v>2</v>
@@ -6908,7 +6904,7 @@
         <v>5</v>
       </c>
       <c r="O117" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="P117" s="3">
         <v>6</v>
@@ -6920,7 +6916,7 @@
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C118" s="1">
         <v>2</v>
@@ -7022,7 +7018,7 @@
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C120" s="1">
         <v>2</v>
@@ -7120,7 +7116,7 @@
         <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C122" s="1">
         <v>2</v>
@@ -7222,7 +7218,7 @@
         <v>123</v>
       </c>
       <c r="B124" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C124" s="1">
         <v>2</v>
@@ -7366,7 +7362,7 @@
         <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C127" s="1">
         <v>2</v>
@@ -7408,7 +7404,7 @@
         <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C128" s="1">
         <v>2</v>
@@ -7506,7 +7502,7 @@
         <v>129</v>
       </c>
       <c r="B130" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C130" s="1">
         <v>2</v>
@@ -7592,7 +7588,7 @@
         <v>7</v>
       </c>
       <c r="O131" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="P131" s="3">
         <v>7</v>
@@ -7609,7 +7605,7 @@
         <v>131</v>
       </c>
       <c r="B132" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C132" s="1">
         <v>2</v>
@@ -7693,7 +7689,7 @@
         <v>0.3</v>
       </c>
       <c r="M133" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N133">
         <v>8</v>
@@ -7796,7 +7792,7 @@
         <v>0.2</v>
       </c>
       <c r="M135" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="N135">
         <v>6</v>
@@ -7810,7 +7806,7 @@
         <v>135</v>
       </c>
       <c r="B136" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C136" s="1">
         <v>2</v>
@@ -7857,7 +7853,7 @@
         <v>136</v>
       </c>
       <c r="B137" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C137" s="1">
         <v>2</v>
@@ -7955,7 +7951,7 @@
         <v>138</v>
       </c>
       <c r="B139" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C139" s="1">
         <v>1</v>
@@ -8006,7 +8002,7 @@
         <v>139</v>
       </c>
       <c r="B140" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C140" s="1">
         <v>2</v>
@@ -8053,7 +8049,7 @@
         <v>140</v>
       </c>
       <c r="B141" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C141" s="1">
         <v>2</v>
@@ -8147,7 +8143,7 @@
         <v>142</v>
       </c>
       <c r="B143" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C143" s="1">
         <v>2</v>
@@ -8198,7 +8194,7 @@
         <v>143</v>
       </c>
       <c r="B144" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C144" s="1">
         <v>2</v>
@@ -8237,7 +8233,7 @@
         <v>5</v>
       </c>
       <c r="O144" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P144" s="3">
         <v>3</v>
@@ -8249,7 +8245,7 @@
         <v>144</v>
       </c>
       <c r="B145" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C145" s="1">
         <v>2</v>
@@ -8333,7 +8329,7 @@
         <v>0.5</v>
       </c>
       <c r="M146" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="N146" s="3">
         <v>6</v>
@@ -8350,7 +8346,7 @@
         <v>146</v>
       </c>
       <c r="B147" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C147" s="1">
         <v>2</v>
@@ -8401,7 +8397,7 @@
         <v>147</v>
       </c>
       <c r="B148" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C148" s="1">
         <v>1</v>
@@ -8440,7 +8436,7 @@
         <v>5</v>
       </c>
       <c r="O148" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P148" s="3">
         <v>5</v>
@@ -8452,7 +8448,7 @@
         <v>148</v>
       </c>
       <c r="B149" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C149" s="1">
         <v>2</v>
@@ -8527,7 +8523,7 @@
     <col min="2" max="2" width="14.53125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.1328125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.06640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="143.796875" customWidth="1"/>
+    <col min="5" max="5" width="236.86328125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="21.19921875" customWidth="1"/>
     <col min="7" max="7" width="18.265625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="18.33203125" bestFit="1" customWidth="1"/>
@@ -8538,7 +8534,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>2</v>
@@ -8547,16 +8543,16 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.4">
@@ -8573,10 +8569,10 @@
         <v>29</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F2">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -8599,16 +8595,16 @@
         <v>29</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.4">
@@ -8625,7 +8621,7 @@
         <v>24</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F4">
         <v>8</v>
@@ -8642,7 +8638,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C5" s="1">
         <v>1</v>
@@ -8651,10 +8647,10 @@
         <v>28</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -8677,7 +8673,7 @@
         <v>22</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F6">
         <v>8</v>
@@ -8703,13 +8699,13 @@
         <v>32</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="G7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H7">
         <v>8</v>
@@ -8720,7 +8716,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C8" s="1">
         <v>2</v>
@@ -8729,16 +8725,16 @@
         <v>21</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G8">
         <v>8</v>
       </c>
       <c r="H8">
-        <v>8</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.4">
@@ -8755,13 +8751,13 @@
         <v>29</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F9">
+        <v>1.5</v>
+      </c>
+      <c r="G9">
         <v>3</v>
-      </c>
-      <c r="G9">
-        <v>8</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -8781,16 +8777,16 @@
         <v>27</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H10">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.4">
@@ -8807,13 +8803,13 @@
         <v>32</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G11">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -8833,13 +8829,13 @@
         <v>29</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F12">
         <v>5</v>
       </c>
       <c r="G12">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -8859,13 +8855,13 @@
         <v>23</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F13">
         <v>5</v>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H13">
         <v>0</v>
@@ -8885,13 +8881,13 @@
         <v>21</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F14">
         <v>5</v>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -8902,7 +8898,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C15" s="1">
         <v>2</v>
@@ -8911,16 +8907,16 @@
         <v>22</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F15">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="G15">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="H15">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.4">
@@ -8937,7 +8933,7 @@
         <v>25</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F16">
         <v>8</v>
@@ -8954,7 +8950,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C17" s="1">
         <v>2</v>
@@ -8963,16 +8959,16 @@
         <v>29</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H17">
-        <v>8</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.4">
@@ -8989,7 +8985,7 @@
         <v>22</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F18">
         <v>3</v>
@@ -9015,7 +9011,7 @@
         <v>20</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F19">
         <v>5</v>
@@ -9032,7 +9028,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C20" s="1">
         <v>1</v>
@@ -9041,7 +9037,7 @@
         <v>30</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F20">
         <v>8</v>
@@ -9067,13 +9063,13 @@
         <v>19</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G21">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H21">
         <v>0</v>
@@ -9084,7 +9080,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C22" s="1">
         <v>1</v>
@@ -9093,7 +9089,7 @@
         <v>21</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F22">
         <v>8</v>
@@ -9110,7 +9106,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C23" s="1">
         <v>2</v>
@@ -9119,7 +9115,7 @@
         <v>24</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F23">
         <v>3</v>
@@ -9145,13 +9141,13 @@
         <v>20</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F24">
         <v>5</v>
       </c>
       <c r="G24">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H24">
         <v>0</v>
@@ -9171,10 +9167,10 @@
         <v>20</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F25">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G25">
         <v>8</v>
@@ -9188,7 +9184,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C26" s="1">
         <v>2</v>
@@ -9197,13 +9193,13 @@
         <v>19</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F26">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="G26">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="H26">
         <v>0</v>
@@ -9223,7 +9219,7 @@
         <v>41</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F27">
         <v>5</v>
@@ -9240,7 +9236,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C28" s="1">
         <v>2</v>
@@ -9249,7 +9245,7 @@
         <v>30</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F28">
         <v>8</v>
@@ -9266,7 +9262,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C29" s="1">
         <v>1</v>
@@ -9275,10 +9271,10 @@
         <v>39</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F29">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G29">
         <v>8</v>
@@ -9292,7 +9288,7 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C30" s="1">
         <v>2</v>
@@ -9301,13 +9297,13 @@
         <v>20</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F30">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="G30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H30">
         <v>10</v>
@@ -9318,7 +9314,7 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C31" s="1">
         <v>1</v>
@@ -9327,7 +9323,7 @@
         <v>33</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F31">
         <v>5</v>
@@ -9353,16 +9349,16 @@
         <v>53</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F32">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="G32">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="H32">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.4">
@@ -9379,7 +9375,7 @@
         <v>30</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F33">
         <v>8</v>
@@ -9396,7 +9392,7 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C34" s="1">
         <v>2</v>
@@ -9405,10 +9401,10 @@
         <v>27</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F34">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="G34">
         <v>0</v>
@@ -9431,10 +9427,10 @@
         <v>33</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F35">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G35">
         <v>0</v>
@@ -9457,13 +9453,13 @@
         <v>20</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F36">
         <v>8</v>
       </c>
       <c r="G36">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="H36">
         <v>0</v>
@@ -9483,16 +9479,16 @@
         <v>19</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F37">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="G37">
         <v>3</v>
       </c>
       <c r="H37">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.4">
@@ -9509,10 +9505,10 @@
         <v>19</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G38">
         <v>8</v>
@@ -9535,13 +9531,13 @@
         <v>19</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F39">
         <v>8</v>
       </c>
       <c r="G39">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="H39">
         <v>8</v>
@@ -9552,7 +9548,7 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C40" s="1">
         <v>2</v>
@@ -9561,13 +9557,13 @@
         <v>58</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F40">
         <v>8</v>
       </c>
       <c r="G40">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H40">
         <v>0</v>
@@ -9587,10 +9583,10 @@
         <v>34</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F41">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G41">
         <v>8</v>
@@ -9613,13 +9609,13 @@
         <v>20</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F42">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="G42">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="H42">
         <v>8</v>
@@ -9630,7 +9626,7 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C43" s="1">
         <v>2</v>
@@ -9639,13 +9635,13 @@
         <v>20</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F43">
         <v>5</v>
       </c>
       <c r="G43">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H43">
         <v>0</v>
@@ -9665,7 +9661,7 @@
         <v>19</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F44">
         <v>8</v>
@@ -9682,7 +9678,7 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C45" s="1">
         <v>2</v>
@@ -9691,7 +9687,7 @@
         <v>19</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F45">
         <v>8</v>
@@ -9708,7 +9704,7 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C46" s="1">
         <v>1</v>
@@ -9717,7 +9713,7 @@
         <v>31</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F46">
         <v>5</v>
@@ -9743,7 +9739,7 @@
         <v>26</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F47">
         <v>5</v>
@@ -9760,7 +9756,7 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C48" s="1">
         <v>2</v>
@@ -9769,7 +9765,7 @@
         <v>48</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F48">
         <v>8</v>
@@ -9778,7 +9774,7 @@
         <v>3</v>
       </c>
       <c r="H48">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.4">
@@ -9786,7 +9782,7 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C49" s="1">
         <v>2</v>
@@ -9795,13 +9791,13 @@
         <v>29</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F49">
         <v>8</v>
       </c>
       <c r="G49">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H49">
         <v>10</v>
@@ -9821,13 +9817,13 @@
         <v>36</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F50">
         <v>5</v>
       </c>
       <c r="G50">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H50">
         <v>0</v>
@@ -9838,7 +9834,7 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C51" s="1">
         <v>2</v>
@@ -9847,7 +9843,7 @@
         <v>31</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F51">
         <v>3</v>
@@ -9873,10 +9869,10 @@
         <v>38</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F52">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G52">
         <v>8</v>
@@ -9890,7 +9886,7 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C53" s="1">
         <v>1</v>
@@ -9899,13 +9895,13 @@
         <v>27</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F53">
         <v>3</v>
       </c>
       <c r="G53">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H53">
         <v>0</v>
@@ -9916,7 +9912,7 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C54" s="1">
         <v>2</v>
@@ -9925,10 +9921,10 @@
         <v>21</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F54">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G54">
         <v>0</v>
@@ -9951,7 +9947,7 @@
         <v>28</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F55">
         <v>8</v>
@@ -9977,10 +9973,10 @@
         <v>65</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F56">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="G56">
         <v>0</v>
@@ -9994,7 +9990,7 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C57" s="1">
         <v>2</v>
@@ -10003,7 +9999,7 @@
         <v>31</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F57">
         <v>5</v>
@@ -10020,7 +10016,7 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C58" s="1">
         <v>2</v>
@@ -10029,13 +10025,13 @@
         <v>32</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F58">
         <v>5</v>
       </c>
       <c r="G58">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H58">
         <v>10</v>
@@ -10046,7 +10042,7 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C59" s="1">
         <v>2</v>
@@ -10055,7 +10051,7 @@
         <v>19</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F59">
         <v>3</v>
@@ -10081,7 +10077,7 @@
         <v>25</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F60">
         <v>8</v>
@@ -10107,7 +10103,7 @@
         <v>28</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F61">
         <v>5</v>
@@ -10124,7 +10120,7 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C62" s="1">
         <v>2</v>
@@ -10133,7 +10129,7 @@
         <v>22</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F62">
         <v>8</v>
@@ -10159,7 +10155,7 @@
         <v>23</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F63">
         <v>5</v>
@@ -10176,7 +10172,7 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C64" s="1">
         <v>2</v>
@@ -10185,7 +10181,7 @@
         <v>19</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F64">
         <v>8</v>
@@ -10211,10 +10207,10 @@
         <v>25</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F65">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="G65">
         <v>8</v>
@@ -10228,7 +10224,7 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C66" s="1">
         <v>2</v>
@@ -10237,13 +10233,13 @@
         <v>20</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F66">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="G66">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="H66">
         <v>0</v>
@@ -10263,7 +10259,7 @@
         <v>21</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F67">
         <v>5</v>
@@ -10280,7 +10276,7 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C68" s="1">
         <v>1</v>
@@ -10289,13 +10285,13 @@
         <v>20</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F68">
         <v>5</v>
       </c>
       <c r="G68">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="H68">
         <v>0</v>
@@ -10306,7 +10302,7 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C69" s="1">
         <v>1</v>
@@ -10315,13 +10311,13 @@
         <v>35</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F69">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G69">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H69">
         <v>0</v>
@@ -10341,13 +10337,13 @@
         <v>21</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F70">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G70">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="H70">
         <v>0</v>
@@ -10367,13 +10363,13 @@
         <v>37</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F71">
         <v>3</v>
       </c>
       <c r="G71">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="H71">
         <v>0</v>
@@ -10393,10 +10389,10 @@
         <v>29</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F72">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="G72">
         <v>0</v>
@@ -10410,7 +10406,7 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C73" s="1">
         <v>2</v>
@@ -10419,10 +10415,10 @@
         <v>32</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F73">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G73">
         <v>8</v>
@@ -10436,7 +10432,7 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C74" s="1">
         <v>1</v>
@@ -10445,10 +10441,10 @@
         <v>25</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F74">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G74">
         <v>8</v>
@@ -10462,7 +10458,7 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C75" s="1">
         <v>1</v>
@@ -10471,7 +10467,7 @@
         <v>32</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F75">
         <v>3</v>
@@ -10497,13 +10493,13 @@
         <v>19</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F76">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G76">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="H76">
         <v>0</v>
@@ -10514,7 +10510,7 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C77" s="1">
         <v>1</v>
@@ -10523,13 +10519,13 @@
         <v>20</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F77">
+        <v>4</v>
+      </c>
+      <c r="G77">
         <v>5</v>
-      </c>
-      <c r="G77">
-        <v>8</v>
       </c>
       <c r="H77">
         <v>0</v>
@@ -10549,13 +10545,13 @@
         <v>19</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F78">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="G78">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="H78">
         <v>8</v>
@@ -10566,7 +10562,7 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C79" s="1">
         <v>2</v>
@@ -10575,10 +10571,10 @@
         <v>52</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F79">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G79">
         <v>0</v>
@@ -10601,13 +10597,13 @@
         <v>34</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F80">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="G80">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H80">
         <v>0</v>
@@ -10618,7 +10614,7 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C81" s="1">
         <v>2</v>
@@ -10627,10 +10623,10 @@
         <v>19</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F81">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G81">
         <v>0</v>
@@ -10644,7 +10640,7 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C82" s="1">
         <v>2</v>
@@ -10653,7 +10649,7 @@
         <v>30</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F82">
         <v>3</v>
@@ -10679,10 +10675,10 @@
         <v>31</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F83">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G83">
         <v>0</v>
@@ -10696,7 +10692,7 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C84" s="1">
         <v>1</v>
@@ -10705,13 +10701,13 @@
         <v>34</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F84">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G84">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="H84">
         <v>0</v>
@@ -10731,7 +10727,7 @@
         <v>20</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F85">
         <v>5</v>
@@ -10748,7 +10744,7 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C86" s="1">
         <v>2</v>
@@ -10757,13 +10753,13 @@
         <v>28</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F86">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G86">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="H86">
         <v>0</v>
@@ -10783,10 +10779,10 @@
         <v>22</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F87">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="G87">
         <v>0</v>
@@ -10809,7 +10805,7 @@
         <v>33</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F88">
         <v>8</v>
@@ -10835,7 +10831,7 @@
         <v>28</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F89">
         <v>5</v>
@@ -10861,10 +10857,10 @@
         <v>21</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F90">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="G90">
         <v>8</v>
@@ -10887,10 +10883,10 @@
         <v>39</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F91">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G91">
         <v>0</v>
@@ -10904,7 +10900,7 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C92" s="1">
         <v>2</v>
@@ -10913,13 +10909,13 @@
         <v>20</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F92">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="G92">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="H92">
         <v>0</v>
@@ -10939,13 +10935,13 @@
         <v>24</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F93">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="G93">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="H93">
         <v>0</v>
@@ -10956,7 +10952,7 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C94" s="1">
         <v>2</v>
@@ -10965,13 +10961,13 @@
         <v>25</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F94">
         <v>5</v>
       </c>
       <c r="G94">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="H94">
         <v>0</v>
@@ -10982,7 +10978,7 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C95" s="1">
         <v>2</v>
@@ -10991,7 +10987,7 @@
         <v>21</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F95">
         <v>8</v>
@@ -11017,13 +11013,13 @@
         <v>46</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F96">
+        <v>3.5</v>
+      </c>
+      <c r="G96">
         <v>3</v>
-      </c>
-      <c r="G96">
-        <v>0</v>
       </c>
       <c r="H96">
         <v>0</v>
@@ -11034,7 +11030,7 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C97" s="1">
         <v>1</v>
@@ -11043,7 +11039,7 @@
         <v>20</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F97">
         <v>8</v>
@@ -11069,13 +11065,13 @@
         <v>20</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F98">
         <v>8</v>
       </c>
       <c r="G98">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H98">
         <v>10</v>
@@ -11086,7 +11082,7 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C99" s="1">
         <v>1</v>
@@ -11095,10 +11091,10 @@
         <v>21</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F99">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G99">
         <v>3</v>
@@ -11121,13 +11117,13 @@
         <v>28</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F100">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="G100">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H100">
         <v>0</v>
@@ -11138,7 +11134,7 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C101" s="1">
         <v>2</v>
@@ -11147,13 +11143,13 @@
         <v>51</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F101">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="G101">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H101">
         <v>0</v>
@@ -11173,7 +11169,7 @@
         <v>21</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F102">
         <v>5</v>
@@ -11199,16 +11195,16 @@
         <v>19</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F103">
         <v>3</v>
       </c>
       <c r="G103">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H103">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.4">
@@ -11216,7 +11212,7 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C104" s="1">
         <v>1</v>
@@ -11225,10 +11221,10 @@
         <v>19</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F104">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G104">
         <v>0</v>
@@ -11242,7 +11238,7 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C105" s="1">
         <v>2</v>
@@ -11251,7 +11247,7 @@
         <v>20</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F105">
         <v>0</v>
@@ -11268,7 +11264,7 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C106" s="1">
         <v>2</v>
@@ -11277,7 +11273,7 @@
         <v>21</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F106">
         <v>5</v>
@@ -11294,7 +11290,7 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C107" s="1">
         <v>2</v>
@@ -11303,10 +11299,10 @@
         <v>25</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F107">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G107">
         <v>8</v>
@@ -11320,7 +11316,7 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C108" s="1">
         <v>1</v>
@@ -11329,13 +11325,13 @@
         <v>31</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="F108">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G108">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="H108">
         <v>10</v>
@@ -11346,7 +11342,7 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C109" s="1">
         <v>1</v>
@@ -11355,10 +11351,10 @@
         <v>34</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F109">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="G109">
         <v>0</v>
@@ -11372,7 +11368,7 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C110" s="1">
         <v>1</v>
@@ -11381,7 +11377,7 @@
         <v>36</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F110">
         <v>5</v>
@@ -11407,16 +11403,16 @@
         <v>20</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="F111">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G111">
         <v>8</v>
       </c>
       <c r="H111">
-        <v>10</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.4">
@@ -11424,7 +11420,7 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C112" s="1">
         <v>2</v>
@@ -11433,10 +11429,10 @@
         <v>24</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="F112">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="G112">
         <v>3</v>
@@ -11450,7 +11446,7 @@
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C113" s="1">
         <v>2</v>
@@ -11459,13 +11455,13 @@
         <v>21</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F113">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="G113">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="H113">
         <v>10</v>
@@ -11485,13 +11481,13 @@
         <v>25</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="F114">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="G114">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="H114">
         <v>0</v>
@@ -11502,7 +11498,7 @@
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C115" s="1">
         <v>2</v>
@@ -11511,7 +11507,7 @@
         <v>32</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F115">
         <v>3</v>
@@ -11537,10 +11533,10 @@
         <v>19</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F116">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="G116">
         <v>0</v>
@@ -11563,10 +11559,10 @@
         <v>19</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="F117">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G117">
         <v>0</v>
@@ -11580,7 +11576,7 @@
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C118" s="1">
         <v>2</v>
@@ -11589,10 +11585,10 @@
         <v>19</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F118">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="G118">
         <v>0</v>
@@ -11615,13 +11611,13 @@
         <v>19</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="F119">
+        <v>2</v>
+      </c>
+      <c r="G119">
         <v>3</v>
-      </c>
-      <c r="G119">
-        <v>0</v>
       </c>
       <c r="H119">
         <v>10</v>
@@ -11632,7 +11628,7 @@
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C120" s="1">
         <v>2</v>
@@ -11641,10 +11637,10 @@
         <v>34</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F120">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="G120">
         <v>8</v>
@@ -11667,10 +11663,10 @@
         <v>20</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F121">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="G121">
         <v>8</v>
@@ -11684,7 +11680,7 @@
         <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C122" s="1">
         <v>2</v>
@@ -11693,10 +11689,10 @@
         <v>25</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F122">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="G122">
         <v>0</v>
@@ -11719,7 +11715,7 @@
         <v>43</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="F123">
         <v>5</v>
@@ -11736,7 +11732,7 @@
         <v>123</v>
       </c>
       <c r="B124" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C124" s="1">
         <v>2</v>
@@ -11745,13 +11741,13 @@
         <v>20</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F124">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G124">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="H124">
         <v>0</v>
@@ -11771,13 +11767,13 @@
         <v>36</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F125">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G125">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H125">
         <v>0</v>
@@ -11797,10 +11793,10 @@
         <v>20</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="F126">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G126">
         <v>0</v>
@@ -11814,7 +11810,7 @@
         <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C127" s="1">
         <v>2</v>
@@ -11823,16 +11819,16 @@
         <v>19</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="F127">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="G127">
         <v>8</v>
       </c>
       <c r="H127">
-        <v>10</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.4">
@@ -11840,7 +11836,7 @@
         <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C128" s="1">
         <v>2</v>
@@ -11849,13 +11845,13 @@
         <v>23</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="F128">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="G128">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="H128">
         <v>0</v>
@@ -11875,10 +11871,10 @@
         <v>31</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F129">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="G129">
         <v>8</v>
@@ -11892,7 +11888,7 @@
         <v>129</v>
       </c>
       <c r="B130" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C130" s="1">
         <v>2</v>
@@ -11901,7 +11897,7 @@
         <v>19</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F130">
         <v>8</v>
@@ -11927,10 +11923,10 @@
         <v>29</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F131">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="G131">
         <v>0</v>
@@ -11944,7 +11940,7 @@
         <v>131</v>
       </c>
       <c r="B132" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C132" s="1">
         <v>2</v>
@@ -11953,16 +11949,16 @@
         <v>33</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F132">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="G132">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="H132">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.4">
@@ -11979,7 +11975,7 @@
         <v>19</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F133">
         <v>3</v>
@@ -12005,7 +12001,7 @@
         <v>25</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F134">
         <v>5</v>
@@ -12031,13 +12027,13 @@
         <v>26</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F135">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G135">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H135">
         <v>0</v>
@@ -12048,7 +12044,7 @@
         <v>135</v>
       </c>
       <c r="B136" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C136" s="1">
         <v>2</v>
@@ -12057,7 +12053,7 @@
         <v>20</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="F136">
         <v>5</v>
@@ -12066,7 +12062,7 @@
         <v>8</v>
       </c>
       <c r="H136">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.4">
@@ -12074,7 +12070,7 @@
         <v>136</v>
       </c>
       <c r="B137" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C137" s="1">
         <v>2</v>
@@ -12083,10 +12079,10 @@
         <v>25</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F137">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G137">
         <v>8</v>
@@ -12109,10 +12105,10 @@
         <v>18</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F138">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="G138">
         <v>0</v>
@@ -12126,7 +12122,7 @@
         <v>138</v>
       </c>
       <c r="B139" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C139" s="1">
         <v>1</v>
@@ -12135,13 +12131,13 @@
         <v>30</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F139">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="G139">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H139">
         <v>0</v>
@@ -12152,7 +12148,7 @@
         <v>139</v>
       </c>
       <c r="B140" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C140" s="1">
         <v>2</v>
@@ -12161,13 +12157,13 @@
         <v>24</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F140">
         <v>8</v>
       </c>
       <c r="G140">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H140">
         <v>8</v>
@@ -12178,7 +12174,7 @@
         <v>140</v>
       </c>
       <c r="B141" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C141" s="1">
         <v>2</v>
@@ -12187,7 +12183,7 @@
         <v>34</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F141">
         <v>5</v>
@@ -12213,10 +12209,10 @@
         <v>33</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="F142">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G142">
         <v>8</v>
@@ -12230,7 +12226,7 @@
         <v>142</v>
       </c>
       <c r="B143" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C143" s="1">
         <v>2</v>
@@ -12239,10 +12235,10 @@
         <v>19</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F143">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G143">
         <v>8</v>
@@ -12256,7 +12252,7 @@
         <v>143</v>
       </c>
       <c r="B144" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C144" s="1">
         <v>2</v>
@@ -12265,7 +12261,7 @@
         <v>21</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="F144">
         <v>5</v>
@@ -12282,7 +12278,7 @@
         <v>144</v>
       </c>
       <c r="B145" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C145" s="1">
         <v>2</v>
@@ -12291,13 +12287,13 @@
         <v>20</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="F145">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G145">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H145">
         <v>0</v>
@@ -12317,10 +12313,10 @@
         <v>19</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F146">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G146">
         <v>0</v>
@@ -12334,7 +12330,7 @@
         <v>146</v>
       </c>
       <c r="B147" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C147" s="1">
         <v>2</v>
@@ -12343,7 +12339,7 @@
         <v>19</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="F147">
         <v>5</v>
@@ -12360,7 +12356,7 @@
         <v>147</v>
       </c>
       <c r="B148" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C148" s="1">
         <v>1</v>
@@ -12369,10 +12365,10 @@
         <v>20</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="F148">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="G148">
         <v>0</v>
@@ -12386,7 +12382,7 @@
         <v>148</v>
       </c>
       <c r="B149" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C149" s="1">
         <v>2</v>
@@ -12395,16 +12391,16 @@
         <v>20</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F149">
+        <v>5.5</v>
+      </c>
+      <c r="G149">
+        <v>9</v>
+      </c>
+      <c r="H149">
         <v>5</v>
-      </c>
-      <c r="G149">
-        <v>10</v>
-      </c>
-      <c r="H149">
-        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/rawdata.xlsx
+++ b/rawdata.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\u_backup\行为实验-终点冥想\Mindfulness\Data and Code V6\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\u_backup\行为实验-终点冥想\Mindfulness\Final version for submission\Revision 1st\Data and Code V6\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9A80A32-D394-419C-B945-BC3D651D455F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06140C8A-F746-4C66-80EF-D58F5805BB57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="rawdata1" sheetId="1" r:id="rId1"/>
@@ -100,10 +100,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>sadness</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>peace</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -124,18 +120,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>sadness with fear</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>anxiety</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>peace with sadness</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>peace with relaxation</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -648,7 +636,19 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>relaxation with sadness</t>
+    <t>melancholy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>peace with melancholy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>relaxation with melancholy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>melancholy with fear</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1076,7 +1076,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>2</v>
@@ -1100,7 +1100,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="K1" s="2" t="s">
         <v>9</v>
@@ -1165,13 +1165,13 @@
         <v>0.4</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>17</v>
+        <v>188</v>
       </c>
       <c r="N2">
         <v>7</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="P2" s="3">
         <v>7</v>
@@ -1216,7 +1216,7 @@
         <v>0.5</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>17</v>
+        <v>188</v>
       </c>
       <c r="N3">
         <v>8</v>
@@ -1263,19 +1263,19 @@
         <v>0.4</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N4">
         <v>7</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>17</v>
+        <v>188</v>
       </c>
       <c r="P4" s="3">
         <v>7</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="R4">
         <v>8</v>
@@ -1286,7 +1286,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C5" s="1">
         <v>1</v>
@@ -1319,13 +1319,13 @@
         <v>0.2</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N5">
         <v>8</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="P5" s="3">
         <v>6</v>
@@ -1370,7 +1370,7 @@
         <v>0.5</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>17</v>
+        <v>188</v>
       </c>
       <c r="N6">
         <v>9</v>
@@ -1417,19 +1417,19 @@
         <v>0</v>
       </c>
       <c r="M7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="N7">
+        <v>7</v>
+      </c>
+      <c r="O7" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="N7">
-        <v>7</v>
-      </c>
-      <c r="O7" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="P7" s="3">
         <v>7</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>17</v>
+        <v>188</v>
       </c>
       <c r="R7">
         <v>7</v>
@@ -1440,7 +1440,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C8" s="1">
         <v>2</v>
@@ -1473,13 +1473,13 @@
         <v>0.8</v>
       </c>
       <c r="M8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="N8">
+        <v>7</v>
+      </c>
+      <c r="O8" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="N8">
-        <v>7</v>
-      </c>
-      <c r="O8" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="P8" s="3">
         <v>7</v>
@@ -1524,13 +1524,13 @@
         <v>0.4</v>
       </c>
       <c r="M9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="N9">
+        <v>7</v>
+      </c>
+      <c r="O9" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="N9">
-        <v>7</v>
-      </c>
-      <c r="O9" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="P9" s="3">
         <v>8</v>
@@ -1575,13 +1575,13 @@
         <v>0.3</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>17</v>
+        <v>188</v>
       </c>
       <c r="N10">
         <v>7</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="P10" s="3">
         <v>6</v>
@@ -1668,7 +1668,7 @@
         <v>0.4</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N12">
         <v>9</v>
@@ -1715,19 +1715,19 @@
         <v>0.2</v>
       </c>
       <c r="M13" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="N13">
+        <v>7</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="P13" s="3">
+        <v>7</v>
+      </c>
+      <c r="Q13" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="N13">
-        <v>7</v>
-      </c>
-      <c r="O13" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="P13" s="3">
-        <v>7</v>
-      </c>
-      <c r="Q13" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="R13">
         <v>6</v>
@@ -1771,19 +1771,19 @@
         <v>0.4</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N14">
         <v>7</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="P14" s="3">
         <v>7</v>
       </c>
       <c r="Q14" s="1" t="s">
-        <v>17</v>
+        <v>188</v>
       </c>
       <c r="R14">
         <v>5</v>
@@ -1794,7 +1794,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C15" s="1">
         <v>2</v>
@@ -1827,7 +1827,7 @@
         <v>0</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N15">
         <v>6</v>
@@ -1874,13 +1874,13 @@
         <v>0.2</v>
       </c>
       <c r="M16" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="N16">
+        <v>7</v>
+      </c>
+      <c r="O16" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="N16">
-        <v>7</v>
-      </c>
-      <c r="O16" s="1" t="s">
-        <v>18</v>
       </c>
       <c r="P16" s="3">
         <v>6</v>
@@ -1892,7 +1892,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C17" s="1">
         <v>2</v>
@@ -1925,13 +1925,13 @@
         <v>0.3</v>
       </c>
       <c r="M17" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="N17">
+        <v>8</v>
+      </c>
+      <c r="O17" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="N17">
-        <v>8</v>
-      </c>
-      <c r="O17" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="P17" s="3">
         <v>6</v>
@@ -1976,7 +1976,7 @@
         <v>0.6</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N18">
         <v>4</v>
@@ -2023,19 +2023,19 @@
         <v>0.4</v>
       </c>
       <c r="M19" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="N19">
+        <v>7</v>
+      </c>
+      <c r="O19" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="N19">
-        <v>7</v>
-      </c>
-      <c r="O19" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="P19" s="3">
         <v>6</v>
       </c>
       <c r="Q19" s="1" t="s">
-        <v>17</v>
+        <v>188</v>
       </c>
       <c r="R19">
         <v>4</v>
@@ -2046,7 +2046,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C20" s="1">
         <v>1</v>
@@ -2079,19 +2079,19 @@
         <v>0.5</v>
       </c>
       <c r="M20" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="N20">
+        <v>8</v>
+      </c>
+      <c r="O20" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="N20">
-        <v>8</v>
-      </c>
-      <c r="O20" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="P20" s="3">
         <v>6</v>
       </c>
       <c r="Q20" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="R20">
         <v>5</v>
@@ -2135,7 +2135,7 @@
         <v>0.4</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>25</v>
+        <v>189</v>
       </c>
       <c r="N21">
         <v>7</v>
@@ -2149,7 +2149,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C22" s="1">
         <v>1</v>
@@ -2182,13 +2182,13 @@
         <v>0</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N22">
         <v>6</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="P22" s="3">
         <v>5</v>
@@ -2200,7 +2200,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C23" s="1">
         <v>2</v>
@@ -2233,7 +2233,7 @@
         <v>0.3</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N23">
         <v>7</v>
@@ -2280,13 +2280,13 @@
         <v>0.4</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>17</v>
+        <v>188</v>
       </c>
       <c r="N24">
         <v>6</v>
       </c>
       <c r="O24" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P24" s="3">
         <v>7</v>
@@ -2331,13 +2331,13 @@
         <v>0.5</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N25">
         <v>7</v>
       </c>
       <c r="O25" s="1" t="s">
-        <v>17</v>
+        <v>188</v>
       </c>
       <c r="P25" s="3">
         <v>5</v>
@@ -2349,7 +2349,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C26" s="1">
         <v>2</v>
@@ -2382,7 +2382,7 @@
         <v>0.5</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N26">
         <v>7</v>
@@ -2429,19 +2429,19 @@
         <v>0.2</v>
       </c>
       <c r="M27" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="N27">
+        <v>8</v>
+      </c>
+      <c r="O27" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="N27">
-        <v>8</v>
-      </c>
-      <c r="O27" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="P27" s="3">
         <v>6</v>
       </c>
       <c r="Q27" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R27">
         <v>9</v>
@@ -2452,7 +2452,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C28" s="1">
         <v>2</v>
@@ -2485,13 +2485,13 @@
         <v>0.2</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N28">
         <v>8</v>
       </c>
       <c r="O28" s="1" t="s">
-        <v>17</v>
+        <v>188</v>
       </c>
       <c r="P28" s="3">
         <v>8</v>
@@ -2503,7 +2503,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C29" s="1">
         <v>1</v>
@@ -2536,7 +2536,7 @@
         <v>0.3</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N29">
         <v>7</v>
@@ -2550,7 +2550,7 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C30" s="1">
         <v>2</v>
@@ -2583,13 +2583,13 @@
         <v>0.4</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N30">
         <v>6</v>
       </c>
       <c r="O30" s="1" t="s">
-        <v>17</v>
+        <v>188</v>
       </c>
       <c r="P30" s="3">
         <v>7</v>
@@ -2601,7 +2601,7 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C31" s="1">
         <v>1</v>
@@ -2634,7 +2634,7 @@
         <v>0.2</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N31">
         <v>7</v>
@@ -2681,7 +2681,7 @@
         <v>0.2</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>17</v>
+        <v>188</v>
       </c>
       <c r="N32">
         <v>7</v>
@@ -2728,13 +2728,13 @@
         <v>0.4</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N33">
         <v>5</v>
       </c>
       <c r="O33" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P33" s="3">
         <v>6</v>
@@ -2746,7 +2746,7 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C34" s="1">
         <v>2</v>
@@ -2779,7 +2779,7 @@
         <v>0.6</v>
       </c>
       <c r="M34" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N34">
         <v>8</v>
@@ -2826,19 +2826,19 @@
         <v>0.4</v>
       </c>
       <c r="M35" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N35">
         <v>6</v>
       </c>
       <c r="O35" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P35" s="3">
         <v>8</v>
       </c>
       <c r="Q35" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R35">
         <v>7</v>
@@ -2882,19 +2882,19 @@
         <v>0.7</v>
       </c>
       <c r="M36" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N36">
         <v>4</v>
       </c>
       <c r="O36" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P36" s="3">
         <v>3</v>
       </c>
       <c r="Q36" s="1" t="s">
-        <v>17</v>
+        <v>188</v>
       </c>
       <c r="R36">
         <v>8</v>
@@ -2938,7 +2938,7 @@
         <v>0.4</v>
       </c>
       <c r="M37" s="1" t="s">
-        <v>25</v>
+        <v>189</v>
       </c>
       <c r="N37">
         <v>6</v>
@@ -2985,7 +2985,7 @@
         <v>0</v>
       </c>
       <c r="M38" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="N38">
         <v>6</v>
@@ -3032,13 +3032,13 @@
         <v>0.6</v>
       </c>
       <c r="M39" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N39">
         <v>6</v>
       </c>
       <c r="O39" s="1" t="s">
-        <v>17</v>
+        <v>188</v>
       </c>
       <c r="P39" s="3">
         <v>4</v>
@@ -3050,7 +3050,7 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C40" s="1">
         <v>2</v>
@@ -3083,13 +3083,13 @@
         <v>0.4</v>
       </c>
       <c r="M40" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N40">
         <v>7</v>
       </c>
       <c r="O40" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="P40" s="3">
         <v>6</v>
@@ -3134,19 +3134,19 @@
         <v>0</v>
       </c>
       <c r="M41" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N41">
         <v>6</v>
       </c>
       <c r="O41" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P41" s="3">
         <v>6</v>
       </c>
       <c r="Q41" s="1" t="s">
-        <v>17</v>
+        <v>188</v>
       </c>
       <c r="R41">
         <v>7</v>
@@ -3190,13 +3190,13 @@
         <v>0.3</v>
       </c>
       <c r="M42" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N42">
         <v>3</v>
       </c>
       <c r="O42" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P42" s="3">
         <v>4</v>
@@ -3208,7 +3208,7 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C43" s="1">
         <v>2</v>
@@ -3241,13 +3241,13 @@
         <v>0</v>
       </c>
       <c r="M43" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N43">
         <v>4</v>
       </c>
       <c r="O43" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="P43" s="3">
         <v>7</v>
@@ -3292,13 +3292,13 @@
         <v>0.4</v>
       </c>
       <c r="M44" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="N44">
+        <v>7</v>
+      </c>
+      <c r="O44" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="N44">
-        <v>7</v>
-      </c>
-      <c r="O44" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="P44" s="3">
         <v>6</v>
@@ -3310,7 +3310,7 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C45" s="1">
         <v>2</v>
@@ -3343,7 +3343,7 @@
         <v>0.7</v>
       </c>
       <c r="M45" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N45">
         <v>8</v>
@@ -3357,7 +3357,7 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C46" s="1">
         <v>1</v>
@@ -3390,7 +3390,7 @@
         <v>0.5</v>
       </c>
       <c r="M46" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N46">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>0.1</v>
       </c>
       <c r="M47" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="N47">
         <v>7</v>
@@ -3451,7 +3451,7 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C48" s="1">
         <v>2</v>
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="M48" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N48">
         <v>6</v>
@@ -3498,7 +3498,7 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C49" s="1">
         <v>2</v>
@@ -3573,7 +3573,7 @@
         <v>0.6</v>
       </c>
       <c r="M50" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N50">
         <v>7</v>
@@ -3587,7 +3587,7 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C51" s="1">
         <v>2</v>
@@ -3620,13 +3620,13 @@
         <v>0.4</v>
       </c>
       <c r="M51" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="N51">
+        <v>8</v>
+      </c>
+      <c r="O51" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="N51">
-        <v>8</v>
-      </c>
-      <c r="O51" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="P51" s="3">
         <v>9</v>
@@ -3671,7 +3671,7 @@
         <v>0.6</v>
       </c>
       <c r="M52" s="1" t="s">
-        <v>23</v>
+        <v>191</v>
       </c>
       <c r="N52">
         <v>7</v>
@@ -3685,7 +3685,7 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C53" s="1">
         <v>1</v>
@@ -3718,13 +3718,13 @@
         <v>0.7</v>
       </c>
       <c r="M53" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N53">
         <v>6</v>
       </c>
       <c r="O53" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="P53" s="3">
         <v>8</v>
@@ -3736,7 +3736,7 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C54" s="1">
         <v>2</v>
@@ -3769,13 +3769,13 @@
         <v>0.8</v>
       </c>
       <c r="M54" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N54">
         <v>6</v>
       </c>
       <c r="O54" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P54" s="3">
         <v>5</v>
@@ -3820,7 +3820,7 @@
         <v>0.9</v>
       </c>
       <c r="M55" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N55">
         <v>9</v>
@@ -3867,13 +3867,13 @@
         <v>0.5</v>
       </c>
       <c r="M56" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N56">
         <v>3</v>
       </c>
       <c r="O56" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P56" s="3">
         <v>4</v>
@@ -3885,7 +3885,7 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C57" s="1">
         <v>2</v>
@@ -3918,7 +3918,7 @@
         <v>0.4</v>
       </c>
       <c r="M57" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="N57">
         <v>9</v>
@@ -3932,7 +3932,7 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C58" s="1">
         <v>2</v>
@@ -3965,13 +3965,13 @@
         <v>0.5</v>
       </c>
       <c r="M58" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N58">
         <v>6</v>
       </c>
       <c r="O58" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P58" s="3">
         <v>4</v>
@@ -3983,7 +3983,7 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C59" s="1">
         <v>2</v>
@@ -4016,19 +4016,19 @@
         <v>0.2</v>
       </c>
       <c r="M59" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="N59">
         <v>6</v>
       </c>
       <c r="O59" s="1" t="s">
-        <v>17</v>
+        <v>188</v>
       </c>
       <c r="P59" s="3">
         <v>5</v>
       </c>
       <c r="Q59" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="R59">
         <v>7</v>
@@ -4072,7 +4072,7 @@
         <v>0.5</v>
       </c>
       <c r="M60" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N60">
         <v>8</v>
@@ -4119,19 +4119,19 @@
         <v>0.2</v>
       </c>
       <c r="M61" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N61">
         <v>7</v>
       </c>
       <c r="O61" s="1" t="s">
-        <v>17</v>
+        <v>188</v>
       </c>
       <c r="P61" s="3">
         <v>6</v>
       </c>
       <c r="Q61" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="R61">
         <v>7</v>
@@ -4142,7 +4142,7 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C62" s="1">
         <v>2</v>
@@ -4175,13 +4175,13 @@
         <v>0.64</v>
       </c>
       <c r="M62" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N62">
         <v>6</v>
       </c>
       <c r="O62" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P62" s="3">
         <v>5</v>
@@ -4226,7 +4226,7 @@
         <v>0</v>
       </c>
       <c r="M63" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N63">
         <v>6</v>
@@ -4240,7 +4240,7 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C64" s="1">
         <v>2</v>
@@ -4273,13 +4273,13 @@
         <v>0.4</v>
       </c>
       <c r="M64" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="N64">
+        <v>7</v>
+      </c>
+      <c r="O64" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="N64">
-        <v>7</v>
-      </c>
-      <c r="O64" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="P64" s="3">
         <v>7</v>
@@ -4324,7 +4324,7 @@
         <v>0.4</v>
       </c>
       <c r="M65" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N65">
         <v>6</v>
@@ -4338,7 +4338,7 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C66" s="1">
         <v>2</v>
@@ -4371,13 +4371,13 @@
         <v>0.7</v>
       </c>
       <c r="M66" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N66">
         <v>7</v>
       </c>
       <c r="O66" s="1" t="s">
-        <v>17</v>
+        <v>188</v>
       </c>
       <c r="P66" s="3">
         <v>4</v>
@@ -4422,7 +4422,7 @@
         <v>0</v>
       </c>
       <c r="M67" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N67">
         <v>7</v>
@@ -4436,7 +4436,7 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C68" s="1">
         <v>1</v>
@@ -4469,13 +4469,13 @@
         <v>0.8</v>
       </c>
       <c r="M68" s="1" t="s">
-        <v>17</v>
+        <v>188</v>
       </c>
       <c r="N68">
         <v>7</v>
       </c>
       <c r="O68" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="P68" s="3">
         <v>5</v>
@@ -4487,7 +4487,7 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C69" s="1">
         <v>1</v>
@@ -4562,13 +4562,13 @@
         <v>0.9</v>
       </c>
       <c r="M70" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N70">
         <v>7</v>
       </c>
       <c r="O70" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="P70" s="3">
         <v>7</v>
@@ -4613,19 +4613,19 @@
         <v>0.8</v>
       </c>
       <c r="M71" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N71">
         <v>7</v>
       </c>
       <c r="O71" s="1" t="s">
-        <v>17</v>
+        <v>188</v>
       </c>
       <c r="P71" s="3">
         <v>5</v>
       </c>
       <c r="Q71" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="R71">
         <v>7</v>
@@ -4669,7 +4669,7 @@
         <v>0.2</v>
       </c>
       <c r="M72" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N72">
         <v>8</v>
@@ -4683,7 +4683,7 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C73" s="1">
         <v>2</v>
@@ -4716,13 +4716,13 @@
         <v>0.6</v>
       </c>
       <c r="M73" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="N73">
+        <v>7</v>
+      </c>
+      <c r="O73" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="N73">
-        <v>7</v>
-      </c>
-      <c r="O73" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="P73" s="3">
         <v>7</v>
@@ -4734,7 +4734,7 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C74" s="1">
         <v>1</v>
@@ -4767,13 +4767,13 @@
         <v>0</v>
       </c>
       <c r="M74" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="N74">
+        <v>8</v>
+      </c>
+      <c r="O74" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="N74">
-        <v>8</v>
-      </c>
-      <c r="O74" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="P74" s="3">
         <v>9</v>
@@ -4785,7 +4785,7 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C75" s="1">
         <v>1</v>
@@ -4818,13 +4818,13 @@
         <v>0.3</v>
       </c>
       <c r="M75" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="N75">
+        <v>7</v>
+      </c>
+      <c r="O75" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="N75">
-        <v>7</v>
-      </c>
-      <c r="O75" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="P75" s="3">
         <v>8</v>
@@ -4869,13 +4869,13 @@
         <v>0.2</v>
       </c>
       <c r="M76" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N76">
         <v>5</v>
       </c>
       <c r="O76" s="1" t="s">
-        <v>17</v>
+        <v>188</v>
       </c>
       <c r="P76" s="3">
         <v>3</v>
@@ -4887,7 +4887,7 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C77" s="1">
         <v>1</v>
@@ -4962,7 +4962,7 @@
         <v>0.2</v>
       </c>
       <c r="M78" s="1" t="s">
-        <v>25</v>
+        <v>189</v>
       </c>
       <c r="N78">
         <v>6</v>
@@ -4976,7 +4976,7 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C79" s="1">
         <v>2</v>
@@ -5009,13 +5009,13 @@
         <v>0.6</v>
       </c>
       <c r="M79" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="N79">
+        <v>8</v>
+      </c>
+      <c r="O79" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="N79">
-        <v>8</v>
-      </c>
-      <c r="O79" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="P79" s="3">
         <v>8</v>
@@ -5060,19 +5060,19 @@
         <v>0.4</v>
       </c>
       <c r="M80" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="N80">
+        <v>8</v>
+      </c>
+      <c r="O80" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="N80">
-        <v>8</v>
-      </c>
-      <c r="O80" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="P80" s="3">
         <v>7</v>
       </c>
       <c r="Q80" s="1" t="s">
-        <v>17</v>
+        <v>188</v>
       </c>
       <c r="R80">
         <v>8</v>
@@ -5083,7 +5083,7 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C81" s="1">
         <v>2</v>
@@ -5116,13 +5116,13 @@
         <v>0.7</v>
       </c>
       <c r="M81" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N81">
         <v>5</v>
       </c>
       <c r="O81" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P81" s="3">
         <v>5</v>
@@ -5134,7 +5134,7 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C82" s="1">
         <v>2</v>
@@ -5167,13 +5167,13 @@
         <v>0.7</v>
       </c>
       <c r="M82" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="N82">
+        <v>7</v>
+      </c>
+      <c r="O82" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="N82">
-        <v>7</v>
-      </c>
-      <c r="O82" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="P82" s="3">
         <v>7</v>
@@ -5218,13 +5218,13 @@
         <v>0.5</v>
       </c>
       <c r="M83" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N83">
         <v>9</v>
       </c>
       <c r="O83" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P83" s="3">
         <v>8</v>
@@ -5236,7 +5236,7 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C84" s="1">
         <v>1</v>
@@ -5269,19 +5269,19 @@
         <v>0.4</v>
       </c>
       <c r="M84" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N84">
         <v>8</v>
       </c>
       <c r="O84" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="P84" s="3">
+        <v>8</v>
+      </c>
+      <c r="Q84" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="P84" s="3">
-        <v>8</v>
-      </c>
-      <c r="Q84" s="1" t="s">
-        <v>18</v>
       </c>
       <c r="R84">
         <v>9</v>
@@ -5325,19 +5325,19 @@
         <v>0.6</v>
       </c>
       <c r="M85" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N85">
         <v>8</v>
       </c>
       <c r="O85" s="1" t="s">
-        <v>17</v>
+        <v>188</v>
       </c>
       <c r="P85" s="3">
         <v>8</v>
       </c>
       <c r="Q85" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="R85">
         <v>7</v>
@@ -5348,7 +5348,7 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C86" s="1">
         <v>2</v>
@@ -5381,7 +5381,7 @@
         <v>0.6</v>
       </c>
       <c r="M86" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N86">
         <v>7</v>
@@ -5428,7 +5428,7 @@
         <v>0.3</v>
       </c>
       <c r="M87" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="N87">
         <v>8</v>
@@ -5475,7 +5475,7 @@
         <v>0.6</v>
       </c>
       <c r="M88" s="1" t="s">
-        <v>17</v>
+        <v>188</v>
       </c>
       <c r="N88">
         <v>8</v>
@@ -5564,13 +5564,13 @@
         <v>0.6</v>
       </c>
       <c r="M90" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N90">
         <v>6</v>
       </c>
       <c r="O90" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P90" s="3">
         <v>7</v>
@@ -5615,13 +5615,13 @@
         <v>0</v>
       </c>
       <c r="M91" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="N91">
+        <v>7</v>
+      </c>
+      <c r="O91" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="N91">
-        <v>7</v>
-      </c>
-      <c r="O91" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="P91" s="3">
         <v>8</v>
@@ -5633,7 +5633,7 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C92" s="1">
         <v>2</v>
@@ -5666,13 +5666,13 @@
         <v>0.6</v>
       </c>
       <c r="M92" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N92">
         <v>5</v>
       </c>
       <c r="O92" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P92" s="3">
         <v>5</v>
@@ -5717,13 +5717,13 @@
         <v>0.6</v>
       </c>
       <c r="M93" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N93">
         <v>7</v>
       </c>
       <c r="O93" s="1" t="s">
-        <v>17</v>
+        <v>188</v>
       </c>
       <c r="P93" s="3">
         <v>7</v>
@@ -5735,7 +5735,7 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C94" s="1">
         <v>2</v>
@@ -5768,7 +5768,7 @@
         <v>0</v>
       </c>
       <c r="M94" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N94">
         <v>8</v>
@@ -5782,7 +5782,7 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C95" s="1">
         <v>2</v>
@@ -5815,13 +5815,13 @@
         <v>0.5</v>
       </c>
       <c r="M95" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N95">
         <v>6</v>
       </c>
       <c r="O95" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P95" s="3">
         <v>7</v>
@@ -5866,13 +5866,13 @@
         <v>0.4</v>
       </c>
       <c r="M96" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N96">
         <v>6</v>
       </c>
       <c r="O96" s="1" t="s">
-        <v>17</v>
+        <v>188</v>
       </c>
       <c r="P96" s="3">
         <v>7</v>
@@ -5884,7 +5884,7 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C97" s="1">
         <v>1</v>
@@ -5917,13 +5917,13 @@
         <v>0.5</v>
       </c>
       <c r="M97" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N97">
         <v>5</v>
       </c>
       <c r="O97" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P97" s="3">
         <v>6</v>
@@ -5968,7 +5968,7 @@
         <v>0</v>
       </c>
       <c r="M98" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N98">
         <v>5</v>
@@ -5982,7 +5982,7 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C99" s="1">
         <v>1</v>
@@ -6015,7 +6015,7 @@
         <v>0.6</v>
       </c>
       <c r="M99" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N99">
         <v>5</v>
@@ -6062,7 +6062,7 @@
         <v>0.4</v>
       </c>
       <c r="M100" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="N100">
         <v>8</v>
@@ -6076,7 +6076,7 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C101" s="1">
         <v>2</v>
@@ -6109,7 +6109,7 @@
         <v>0.4</v>
       </c>
       <c r="M101" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="N101">
         <v>6</v>
@@ -6156,13 +6156,13 @@
         <v>0.66</v>
       </c>
       <c r="M102" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N102">
         <v>9</v>
       </c>
       <c r="O102" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P102" s="3">
         <v>6</v>
@@ -6207,7 +6207,7 @@
         <v>0</v>
       </c>
       <c r="M103" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N103">
         <v>4</v>
@@ -6221,7 +6221,7 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C104" s="1">
         <v>1</v>
@@ -6254,13 +6254,13 @@
         <v>0.6</v>
       </c>
       <c r="M104" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N104">
         <v>6</v>
       </c>
       <c r="O104" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="P104" s="3">
         <v>6</v>
@@ -6272,7 +6272,7 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C105" s="1">
         <v>2</v>
@@ -6305,13 +6305,13 @@
         <v>0</v>
       </c>
       <c r="M105" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N105">
         <v>5</v>
       </c>
       <c r="O105" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P105" s="3">
         <v>4</v>
@@ -6323,7 +6323,7 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C106" s="1">
         <v>2</v>
@@ -6356,7 +6356,7 @@
         <v>0</v>
       </c>
       <c r="M106" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N106">
         <v>6</v>
@@ -6370,7 +6370,7 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C107" s="1">
         <v>2</v>
@@ -6403,7 +6403,7 @@
         <v>0.5</v>
       </c>
       <c r="M107" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N107">
         <v>7</v>
@@ -6417,7 +6417,7 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C108" s="1">
         <v>1</v>
@@ -6450,13 +6450,13 @@
         <v>0</v>
       </c>
       <c r="M108" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="N108">
+        <v>7</v>
+      </c>
+      <c r="O108" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="N108">
-        <v>7</v>
-      </c>
-      <c r="O108" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="P108" s="3">
         <v>7</v>
@@ -6468,7 +6468,7 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C109" s="1">
         <v>1</v>
@@ -6501,7 +6501,7 @@
         <v>0</v>
       </c>
       <c r="M109" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N109">
         <v>7</v>
@@ -6515,7 +6515,7 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C110" s="1">
         <v>1</v>
@@ -6548,19 +6548,19 @@
         <v>0.2</v>
       </c>
       <c r="M110" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="N110">
+        <v>7</v>
+      </c>
+      <c r="O110" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="N110">
-        <v>7</v>
-      </c>
-      <c r="O110" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="P110" s="3">
         <v>7</v>
       </c>
       <c r="Q110" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="R110">
         <v>6</v>
@@ -6604,13 +6604,13 @@
         <v>0.4</v>
       </c>
       <c r="M111" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N111">
         <v>9</v>
       </c>
       <c r="O111" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P111" s="3">
         <v>8</v>
@@ -6622,7 +6622,7 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C112" s="1">
         <v>2</v>
@@ -6655,7 +6655,7 @@
         <v>0.7</v>
       </c>
       <c r="M112" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N112">
         <v>6</v>
@@ -6669,7 +6669,7 @@
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C113" s="1">
         <v>2</v>
@@ -6702,7 +6702,7 @@
         <v>0.8</v>
       </c>
       <c r="M113" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N113">
         <v>5</v>
@@ -6749,13 +6749,13 @@
         <v>0.7</v>
       </c>
       <c r="M114" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N114">
         <v>6</v>
       </c>
       <c r="O114" s="1" t="s">
-        <v>17</v>
+        <v>188</v>
       </c>
       <c r="P114" s="3">
         <v>7</v>
@@ -6767,7 +6767,7 @@
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C115" s="1">
         <v>2</v>
@@ -6800,13 +6800,13 @@
         <v>0.4</v>
       </c>
       <c r="M115" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N115">
         <v>4</v>
       </c>
       <c r="O115" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P115" s="3">
         <v>5</v>
@@ -6851,7 +6851,7 @@
         <v>0.6</v>
       </c>
       <c r="M116" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N116">
         <v>6</v>
@@ -6898,13 +6898,13 @@
         <v>0.4</v>
       </c>
       <c r="M117" s="1" t="s">
-        <v>17</v>
+        <v>188</v>
       </c>
       <c r="N117">
         <v>5</v>
       </c>
       <c r="O117" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="P117" s="3">
         <v>6</v>
@@ -6916,7 +6916,7 @@
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C118" s="1">
         <v>2</v>
@@ -6949,13 +6949,13 @@
         <v>0.9</v>
       </c>
       <c r="M118" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N118">
         <v>5</v>
       </c>
       <c r="O118" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P118" s="3">
         <v>3</v>
@@ -7000,13 +7000,13 @@
         <v>0.2</v>
       </c>
       <c r="M119" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="N119">
+        <v>8</v>
+      </c>
+      <c r="O119" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="N119">
-        <v>8</v>
-      </c>
-      <c r="O119" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="P119" s="3">
         <v>5</v>
@@ -7018,7 +7018,7 @@
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C120" s="1">
         <v>2</v>
@@ -7051,7 +7051,7 @@
         <v>0.4</v>
       </c>
       <c r="M120" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N120">
         <v>8</v>
@@ -7098,13 +7098,13 @@
         <v>0.6</v>
       </c>
       <c r="M121" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N121">
         <v>6</v>
       </c>
       <c r="O121" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P121" s="3">
         <v>5</v>
@@ -7116,7 +7116,7 @@
         <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C122" s="1">
         <v>2</v>
@@ -7149,13 +7149,13 @@
         <v>0.76</v>
       </c>
       <c r="M122" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="N122">
+        <v>7</v>
+      </c>
+      <c r="O122" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="N122">
-        <v>7</v>
-      </c>
-      <c r="O122" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="P122" s="3">
         <v>7</v>
@@ -7200,13 +7200,13 @@
         <v>0.2</v>
       </c>
       <c r="M123" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="N123">
+        <v>7</v>
+      </c>
+      <c r="O123" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="N123">
-        <v>7</v>
-      </c>
-      <c r="O123" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="P123" s="3">
         <v>8</v>
@@ -7218,7 +7218,7 @@
         <v>123</v>
       </c>
       <c r="B124" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C124" s="1">
         <v>2</v>
@@ -7293,13 +7293,13 @@
         <v>0.2</v>
       </c>
       <c r="M125" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="N125">
+        <v>8</v>
+      </c>
+      <c r="O125" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="N125">
-        <v>8</v>
-      </c>
-      <c r="O125" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="P125" s="3">
         <v>3</v>
@@ -7344,13 +7344,13 @@
         <v>0.5</v>
       </c>
       <c r="M126" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N126">
         <v>5</v>
       </c>
       <c r="O126" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P126" s="3">
         <v>5</v>
@@ -7362,7 +7362,7 @@
         <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C127" s="1">
         <v>2</v>
@@ -7404,7 +7404,7 @@
         <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C128" s="1">
         <v>2</v>
@@ -7437,13 +7437,13 @@
         <v>0.36</v>
       </c>
       <c r="M128" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N128">
         <v>5</v>
       </c>
       <c r="O128" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P128" s="3">
         <v>5</v>
@@ -7488,7 +7488,7 @@
         <v>0.84</v>
       </c>
       <c r="M129" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N129">
         <v>7</v>
@@ -7502,7 +7502,7 @@
         <v>129</v>
       </c>
       <c r="B130" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C130" s="1">
         <v>2</v>
@@ -7535,7 +7535,7 @@
         <v>0.4</v>
       </c>
       <c r="M130" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N130">
         <v>6</v>
@@ -7582,19 +7582,19 @@
         <v>0.6</v>
       </c>
       <c r="M131" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N131">
         <v>7</v>
       </c>
       <c r="O131" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="P131" s="3">
         <v>7</v>
       </c>
       <c r="Q131" s="1" t="s">
-        <v>17</v>
+        <v>188</v>
       </c>
       <c r="R131">
         <v>8</v>
@@ -7605,7 +7605,7 @@
         <v>131</v>
       </c>
       <c r="B132" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C132" s="1">
         <v>2</v>
@@ -7638,13 +7638,13 @@
         <v>0.8</v>
       </c>
       <c r="M132" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="N132">
+        <v>8</v>
+      </c>
+      <c r="O132" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="N132">
-        <v>8</v>
-      </c>
-      <c r="O132" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="P132" s="3">
         <v>8</v>
@@ -7689,7 +7689,7 @@
         <v>0.3</v>
       </c>
       <c r="M133" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="N133">
         <v>8</v>
@@ -7736,19 +7736,19 @@
         <v>1</v>
       </c>
       <c r="M134" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="N134">
+        <v>7</v>
+      </c>
+      <c r="O134" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="N134">
-        <v>7</v>
-      </c>
-      <c r="O134" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="P134" s="3">
         <v>6</v>
       </c>
       <c r="Q134" s="1" t="s">
-        <v>17</v>
+        <v>188</v>
       </c>
       <c r="R134">
         <v>7</v>
@@ -7792,7 +7792,7 @@
         <v>0.2</v>
       </c>
       <c r="M135" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="N135">
         <v>6</v>
@@ -7806,7 +7806,7 @@
         <v>135</v>
       </c>
       <c r="B136" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C136" s="1">
         <v>2</v>
@@ -7839,7 +7839,7 @@
         <v>0.8</v>
       </c>
       <c r="M136" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N136">
         <v>6</v>
@@ -7853,7 +7853,7 @@
         <v>136</v>
       </c>
       <c r="B137" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C137" s="1">
         <v>2</v>
@@ -7886,13 +7886,13 @@
         <v>0.6</v>
       </c>
       <c r="M137" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="N137">
+        <v>7</v>
+      </c>
+      <c r="O137" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="N137">
-        <v>7</v>
-      </c>
-      <c r="O137" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="P137" s="3">
         <v>6</v>
@@ -7937,7 +7937,7 @@
         <v>0.7</v>
       </c>
       <c r="M138" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N138">
         <v>7</v>
@@ -7951,7 +7951,7 @@
         <v>138</v>
       </c>
       <c r="B139" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C139" s="1">
         <v>1</v>
@@ -7984,13 +7984,13 @@
         <v>0.6</v>
       </c>
       <c r="M139" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N139">
         <v>7</v>
       </c>
       <c r="O139" s="1" t="s">
-        <v>17</v>
+        <v>188</v>
       </c>
       <c r="P139" s="3">
         <v>3</v>
@@ -8002,7 +8002,7 @@
         <v>139</v>
       </c>
       <c r="B140" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C140" s="1">
         <v>2</v>
@@ -8035,7 +8035,7 @@
         <v>0.4</v>
       </c>
       <c r="M140" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N140">
         <v>6</v>
@@ -8049,7 +8049,7 @@
         <v>140</v>
       </c>
       <c r="B141" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C141" s="1">
         <v>2</v>
@@ -8082,7 +8082,7 @@
         <v>0.8</v>
       </c>
       <c r="M141" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N141">
         <v>7</v>
@@ -8129,7 +8129,7 @@
         <v>0.4</v>
       </c>
       <c r="M142" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N142">
         <v>7</v>
@@ -8143,7 +8143,7 @@
         <v>142</v>
       </c>
       <c r="B143" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C143" s="1">
         <v>2</v>
@@ -8176,13 +8176,13 @@
         <v>0.9</v>
       </c>
       <c r="M143" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N143">
         <v>4</v>
       </c>
       <c r="O143" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="P143" s="3">
         <v>5</v>
@@ -8194,7 +8194,7 @@
         <v>143</v>
       </c>
       <c r="B144" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C144" s="1">
         <v>2</v>
@@ -8227,13 +8227,13 @@
         <v>0.5</v>
       </c>
       <c r="M144" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N144">
         <v>5</v>
       </c>
       <c r="O144" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="P144" s="3">
         <v>3</v>
@@ -8245,7 +8245,7 @@
         <v>144</v>
       </c>
       <c r="B145" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C145" s="1">
         <v>2</v>
@@ -8278,13 +8278,13 @@
         <v>0.3</v>
       </c>
       <c r="M145" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N145">
         <v>6</v>
       </c>
       <c r="O145" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P145" s="3">
         <v>6</v>
@@ -8329,13 +8329,13 @@
         <v>0.5</v>
       </c>
       <c r="M146" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="N146" s="3">
         <v>6</v>
       </c>
       <c r="O146" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P146">
         <v>7</v>
@@ -8346,7 +8346,7 @@
         <v>146</v>
       </c>
       <c r="B147" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C147" s="1">
         <v>2</v>
@@ -8379,13 +8379,13 @@
         <v>0.6</v>
       </c>
       <c r="M147" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N147">
         <v>3</v>
       </c>
       <c r="O147" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P147" s="3">
         <v>4</v>
@@ -8397,7 +8397,7 @@
         <v>147</v>
       </c>
       <c r="B148" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C148" s="1">
         <v>1</v>
@@ -8430,13 +8430,13 @@
         <v>0.6</v>
       </c>
       <c r="M148" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N148">
         <v>5</v>
       </c>
       <c r="O148" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="P148" s="3">
         <v>5</v>
@@ -8448,7 +8448,7 @@
         <v>148</v>
       </c>
       <c r="B149" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C149" s="1">
         <v>2</v>
@@ -8481,13 +8481,13 @@
         <v>0.6</v>
       </c>
       <c r="M149" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N149">
         <v>6</v>
       </c>
       <c r="O149" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="P149" s="3">
         <v>4</v>
@@ -8534,7 +8534,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>2</v>
@@ -8543,16 +8543,16 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.4">
@@ -8569,7 +8569,7 @@
         <v>29</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F2">
         <v>8.5</v>
@@ -8595,7 +8595,7 @@
         <v>29</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F3">
         <v>2</v>
@@ -8621,7 +8621,7 @@
         <v>24</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F4">
         <v>8</v>
@@ -8638,7 +8638,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C5" s="1">
         <v>1</v>
@@ -8647,7 +8647,7 @@
         <v>28</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F5">
         <v>2</v>
@@ -8673,7 +8673,7 @@
         <v>22</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F6">
         <v>8</v>
@@ -8699,7 +8699,7 @@
         <v>32</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F7">
         <v>1.5</v>
@@ -8716,7 +8716,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C8" s="1">
         <v>2</v>
@@ -8725,7 +8725,7 @@
         <v>21</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F8">
         <v>4</v>
@@ -8751,7 +8751,7 @@
         <v>29</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F9">
         <v>1.5</v>
@@ -8777,7 +8777,7 @@
         <v>27</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F10">
         <v>9</v>
@@ -8803,7 +8803,7 @@
         <v>32</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F11">
         <v>2</v>
@@ -8829,7 +8829,7 @@
         <v>29</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -8855,7 +8855,7 @@
         <v>23</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -8881,7 +8881,7 @@
         <v>21</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -8898,7 +8898,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C15" s="1">
         <v>2</v>
@@ -8907,7 +8907,7 @@
         <v>22</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F15">
         <v>6.5</v>
@@ -8933,7 +8933,7 @@
         <v>25</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="F16">
         <v>8</v>
@@ -8950,7 +8950,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C17" s="1">
         <v>2</v>
@@ -8959,7 +8959,7 @@
         <v>29</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="F17">
         <v>2</v>
@@ -8985,7 +8985,7 @@
         <v>22</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F18">
         <v>3</v>
@@ -9011,7 +9011,7 @@
         <v>20</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="F19">
         <v>5</v>
@@ -9028,7 +9028,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C20" s="1">
         <v>1</v>
@@ -9037,7 +9037,7 @@
         <v>30</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F20">
         <v>8</v>
@@ -9063,7 +9063,7 @@
         <v>19</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F21">
         <v>7</v>
@@ -9080,7 +9080,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C22" s="1">
         <v>1</v>
@@ -9089,7 +9089,7 @@
         <v>21</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F22">
         <v>8</v>
@@ -9106,7 +9106,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C23" s="1">
         <v>2</v>
@@ -9115,7 +9115,7 @@
         <v>24</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F23">
         <v>3</v>
@@ -9141,7 +9141,7 @@
         <v>20</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F24">
         <v>5</v>
@@ -9167,7 +9167,7 @@
         <v>20</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F25">
         <v>4</v>
@@ -9184,7 +9184,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C26" s="1">
         <v>2</v>
@@ -9193,7 +9193,7 @@
         <v>19</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="F26">
         <v>4.5</v>
@@ -9219,7 +9219,7 @@
         <v>41</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F27">
         <v>5</v>
@@ -9236,7 +9236,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C28" s="1">
         <v>2</v>
@@ -9245,7 +9245,7 @@
         <v>30</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F28">
         <v>8</v>
@@ -9262,7 +9262,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C29" s="1">
         <v>1</v>
@@ -9271,7 +9271,7 @@
         <v>39</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="F29">
         <v>6</v>
@@ -9288,7 +9288,7 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C30" s="1">
         <v>2</v>
@@ -9297,7 +9297,7 @@
         <v>20</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F30">
         <v>7.5</v>
@@ -9314,7 +9314,7 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C31" s="1">
         <v>1</v>
@@ -9323,7 +9323,7 @@
         <v>33</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="F31">
         <v>5</v>
@@ -9349,7 +9349,7 @@
         <v>53</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="F32">
         <v>8.5</v>
@@ -9375,7 +9375,7 @@
         <v>30</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F33">
         <v>8</v>
@@ -9392,7 +9392,7 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C34" s="1">
         <v>2</v>
@@ -9401,7 +9401,7 @@
         <v>27</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F34">
         <v>8.5</v>
@@ -9427,7 +9427,7 @@
         <v>33</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F35">
         <v>2</v>
@@ -9453,7 +9453,7 @@
         <v>20</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="F36">
         <v>8</v>
@@ -9479,7 +9479,7 @@
         <v>19</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="F37">
         <v>8.5</v>
@@ -9505,7 +9505,7 @@
         <v>19</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F38">
         <v>6</v>
@@ -9531,7 +9531,7 @@
         <v>19</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="F39">
         <v>8</v>
@@ -9548,7 +9548,7 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C40" s="1">
         <v>2</v>
@@ -9557,7 +9557,7 @@
         <v>58</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="F40">
         <v>8</v>
@@ -9583,7 +9583,7 @@
         <v>34</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="F41">
         <v>7</v>
@@ -9609,7 +9609,7 @@
         <v>20</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="F42">
         <v>7.5</v>
@@ -9626,7 +9626,7 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C43" s="1">
         <v>2</v>
@@ -9635,7 +9635,7 @@
         <v>20</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="F43">
         <v>5</v>
@@ -9661,7 +9661,7 @@
         <v>19</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="F44">
         <v>8</v>
@@ -9678,7 +9678,7 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C45" s="1">
         <v>2</v>
@@ -9687,7 +9687,7 @@
         <v>19</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F45">
         <v>8</v>
@@ -9704,7 +9704,7 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C46" s="1">
         <v>1</v>
@@ -9713,7 +9713,7 @@
         <v>31</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F46">
         <v>5</v>
@@ -9739,7 +9739,7 @@
         <v>26</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F47">
         <v>5</v>
@@ -9756,7 +9756,7 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C48" s="1">
         <v>2</v>
@@ -9765,7 +9765,7 @@
         <v>48</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F48">
         <v>8</v>
@@ -9782,7 +9782,7 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C49" s="1">
         <v>2</v>
@@ -9791,7 +9791,7 @@
         <v>29</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="F49">
         <v>8</v>
@@ -9817,7 +9817,7 @@
         <v>36</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="F50">
         <v>5</v>
@@ -9834,7 +9834,7 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C51" s="1">
         <v>2</v>
@@ -9843,7 +9843,7 @@
         <v>31</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F51">
         <v>3</v>
@@ -9869,7 +9869,7 @@
         <v>38</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="F52">
         <v>7</v>
@@ -9886,7 +9886,7 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C53" s="1">
         <v>1</v>
@@ -9895,7 +9895,7 @@
         <v>27</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="F53">
         <v>3</v>
@@ -9912,7 +9912,7 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C54" s="1">
         <v>2</v>
@@ -9921,7 +9921,7 @@
         <v>21</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="F54">
         <v>9</v>
@@ -9947,7 +9947,7 @@
         <v>28</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F55">
         <v>8</v>
@@ -9973,7 +9973,7 @@
         <v>65</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F56">
         <v>8.5</v>
@@ -9990,7 +9990,7 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C57" s="1">
         <v>2</v>
@@ -9999,7 +9999,7 @@
         <v>31</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F57">
         <v>5</v>
@@ -10016,7 +10016,7 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C58" s="1">
         <v>2</v>
@@ -10025,7 +10025,7 @@
         <v>32</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F58">
         <v>5</v>
@@ -10042,7 +10042,7 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C59" s="1">
         <v>2</v>
@@ -10051,7 +10051,7 @@
         <v>19</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F59">
         <v>3</v>
@@ -10077,7 +10077,7 @@
         <v>25</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="F60">
         <v>8</v>
@@ -10103,7 +10103,7 @@
         <v>28</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F61">
         <v>5</v>
@@ -10120,7 +10120,7 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C62" s="1">
         <v>2</v>
@@ -10129,7 +10129,7 @@
         <v>22</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F62">
         <v>8</v>
@@ -10155,7 +10155,7 @@
         <v>23</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="F63">
         <v>5</v>
@@ -10172,7 +10172,7 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C64" s="1">
         <v>2</v>
@@ -10181,7 +10181,7 @@
         <v>19</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F64">
         <v>8</v>
@@ -10207,7 +10207,7 @@
         <v>25</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="F65">
         <v>1.5</v>
@@ -10224,7 +10224,7 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C66" s="1">
         <v>2</v>
@@ -10233,7 +10233,7 @@
         <v>20</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F66">
         <v>2.5</v>
@@ -10259,7 +10259,7 @@
         <v>21</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="F67">
         <v>5</v>
@@ -10276,7 +10276,7 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C68" s="1">
         <v>1</v>
@@ -10285,7 +10285,7 @@
         <v>20</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F68">
         <v>5</v>
@@ -10302,7 +10302,7 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C69" s="1">
         <v>1</v>
@@ -10311,7 +10311,7 @@
         <v>35</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="F69">
         <v>2</v>
@@ -10337,7 +10337,7 @@
         <v>21</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="F70">
         <v>6</v>
@@ -10363,7 +10363,7 @@
         <v>37</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F71">
         <v>3</v>
@@ -10389,7 +10389,7 @@
         <v>29</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F72">
         <v>7.5</v>
@@ -10406,7 +10406,7 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C73" s="1">
         <v>2</v>
@@ -10415,7 +10415,7 @@
         <v>32</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="F73">
         <v>7</v>
@@ -10432,7 +10432,7 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C74" s="1">
         <v>1</v>
@@ -10441,7 +10441,7 @@
         <v>25</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="F74">
         <v>4</v>
@@ -10458,7 +10458,7 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C75" s="1">
         <v>1</v>
@@ -10467,7 +10467,7 @@
         <v>32</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F75">
         <v>3</v>
@@ -10493,7 +10493,7 @@
         <v>19</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="F76">
         <v>4</v>
@@ -10510,7 +10510,7 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C77" s="1">
         <v>1</v>
@@ -10519,7 +10519,7 @@
         <v>20</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="F77">
         <v>4</v>
@@ -10545,7 +10545,7 @@
         <v>19</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="F78">
         <v>6.5</v>
@@ -10562,7 +10562,7 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C79" s="1">
         <v>2</v>
@@ -10571,7 +10571,7 @@
         <v>52</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="F79">
         <v>7</v>
@@ -10597,7 +10597,7 @@
         <v>34</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F80">
         <v>7.5</v>
@@ -10614,7 +10614,7 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C81" s="1">
         <v>2</v>
@@ -10623,7 +10623,7 @@
         <v>19</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="F81">
         <v>4</v>
@@ -10640,7 +10640,7 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C82" s="1">
         <v>2</v>
@@ -10649,7 +10649,7 @@
         <v>30</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="F82">
         <v>3</v>
@@ -10675,7 +10675,7 @@
         <v>31</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F83">
         <v>2</v>
@@ -10692,7 +10692,7 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C84" s="1">
         <v>1</v>
@@ -10701,7 +10701,7 @@
         <v>34</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="F84">
         <v>7</v>
@@ -10727,7 +10727,7 @@
         <v>20</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="F85">
         <v>5</v>
@@ -10744,7 +10744,7 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C86" s="1">
         <v>2</v>
@@ -10753,7 +10753,7 @@
         <v>28</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F86">
         <v>9</v>
@@ -10779,7 +10779,7 @@
         <v>22</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F87">
         <v>5.5</v>
@@ -10805,7 +10805,7 @@
         <v>33</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="F88">
         <v>8</v>
@@ -10831,7 +10831,7 @@
         <v>28</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="F89">
         <v>5</v>
@@ -10857,7 +10857,7 @@
         <v>21</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="F90">
         <v>5.5</v>
@@ -10883,7 +10883,7 @@
         <v>39</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="F91">
         <v>8</v>
@@ -10900,7 +10900,7 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C92" s="1">
         <v>2</v>
@@ -10909,7 +10909,7 @@
         <v>20</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="F92">
         <v>7.5</v>
@@ -10935,7 +10935,7 @@
         <v>24</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="F93">
         <v>5.5</v>
@@ -10952,7 +10952,7 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C94" s="1">
         <v>2</v>
@@ -10961,7 +10961,7 @@
         <v>25</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F94">
         <v>5</v>
@@ -10978,7 +10978,7 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C95" s="1">
         <v>2</v>
@@ -10987,7 +10987,7 @@
         <v>21</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="F95">
         <v>8</v>
@@ -11013,7 +11013,7 @@
         <v>46</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F96">
         <v>3.5</v>
@@ -11030,7 +11030,7 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C97" s="1">
         <v>1</v>
@@ -11039,7 +11039,7 @@
         <v>20</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="F97">
         <v>8</v>
@@ -11065,7 +11065,7 @@
         <v>20</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="F98">
         <v>8</v>
@@ -11082,7 +11082,7 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C99" s="1">
         <v>1</v>
@@ -11091,7 +11091,7 @@
         <v>21</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="F99">
         <v>4</v>
@@ -11117,7 +11117,7 @@
         <v>28</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="F100">
         <v>5.5</v>
@@ -11134,7 +11134,7 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C101" s="1">
         <v>2</v>
@@ -11143,7 +11143,7 @@
         <v>51</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="F101">
         <v>2.5</v>
@@ -11169,7 +11169,7 @@
         <v>21</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F102">
         <v>5</v>
@@ -11195,7 +11195,7 @@
         <v>19</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F103">
         <v>3</v>
@@ -11212,7 +11212,7 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C104" s="1">
         <v>1</v>
@@ -11221,7 +11221,7 @@
         <v>19</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F104">
         <v>7</v>
@@ -11238,7 +11238,7 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C105" s="1">
         <v>2</v>
@@ -11247,7 +11247,7 @@
         <v>20</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F105">
         <v>0</v>
@@ -11264,7 +11264,7 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C106" s="1">
         <v>2</v>
@@ -11273,7 +11273,7 @@
         <v>21</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="F106">
         <v>5</v>
@@ -11290,7 +11290,7 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C107" s="1">
         <v>2</v>
@@ -11299,7 +11299,7 @@
         <v>25</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="F107">
         <v>2</v>
@@ -11316,7 +11316,7 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C108" s="1">
         <v>1</v>
@@ -11325,7 +11325,7 @@
         <v>31</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F108">
         <v>6</v>
@@ -11342,7 +11342,7 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C109" s="1">
         <v>1</v>
@@ -11351,7 +11351,7 @@
         <v>34</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="F109">
         <v>5.5</v>
@@ -11368,7 +11368,7 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C110" s="1">
         <v>1</v>
@@ -11377,7 +11377,7 @@
         <v>36</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F110">
         <v>5</v>
@@ -11403,7 +11403,7 @@
         <v>20</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="F111">
         <v>4</v>
@@ -11420,7 +11420,7 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C112" s="1">
         <v>2</v>
@@ -11429,7 +11429,7 @@
         <v>24</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="F112">
         <v>5.5</v>
@@ -11446,7 +11446,7 @@
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C113" s="1">
         <v>2</v>
@@ -11455,7 +11455,7 @@
         <v>21</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="F113">
         <v>5.5</v>
@@ -11481,7 +11481,7 @@
         <v>25</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="F114">
         <v>5.5</v>
@@ -11498,7 +11498,7 @@
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C115" s="1">
         <v>2</v>
@@ -11507,7 +11507,7 @@
         <v>32</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F115">
         <v>3</v>
@@ -11533,7 +11533,7 @@
         <v>19</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="F116">
         <v>6.5</v>
@@ -11559,7 +11559,7 @@
         <v>19</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="F117">
         <v>2</v>
@@ -11576,7 +11576,7 @@
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C118" s="1">
         <v>2</v>
@@ -11585,7 +11585,7 @@
         <v>19</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="F118">
         <v>5.5</v>
@@ -11611,7 +11611,7 @@
         <v>19</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="F119">
         <v>2</v>
@@ -11628,7 +11628,7 @@
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C120" s="1">
         <v>2</v>
@@ -11637,7 +11637,7 @@
         <v>34</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F120">
         <v>5.5</v>
@@ -11663,7 +11663,7 @@
         <v>20</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="F121">
         <v>6.5</v>
@@ -11680,7 +11680,7 @@
         <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C122" s="1">
         <v>2</v>
@@ -11689,7 +11689,7 @@
         <v>25</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="F122">
         <v>8.5</v>
@@ -11715,7 +11715,7 @@
         <v>43</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="F123">
         <v>5</v>
@@ -11732,7 +11732,7 @@
         <v>123</v>
       </c>
       <c r="B124" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C124" s="1">
         <v>2</v>
@@ -11741,7 +11741,7 @@
         <v>20</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="F124">
         <v>4</v>
@@ -11767,7 +11767,7 @@
         <v>36</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="F125">
         <v>7</v>
@@ -11793,7 +11793,7 @@
         <v>20</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="F126">
         <v>2</v>
@@ -11810,7 +11810,7 @@
         <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C127" s="1">
         <v>2</v>
@@ -11819,7 +11819,7 @@
         <v>19</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="F127">
         <v>3.5</v>
@@ -11836,7 +11836,7 @@
         <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C128" s="1">
         <v>2</v>
@@ -11845,7 +11845,7 @@
         <v>23</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F128">
         <v>8.5</v>
@@ -11871,7 +11871,7 @@
         <v>31</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="F129">
         <v>5.5</v>
@@ -11888,7 +11888,7 @@
         <v>129</v>
       </c>
       <c r="B130" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C130" s="1">
         <v>2</v>
@@ -11897,7 +11897,7 @@
         <v>19</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="F130">
         <v>8</v>
@@ -11923,7 +11923,7 @@
         <v>29</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="F131">
         <v>8.5</v>
@@ -11940,7 +11940,7 @@
         <v>131</v>
       </c>
       <c r="B132" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C132" s="1">
         <v>2</v>
@@ -11949,7 +11949,7 @@
         <v>33</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="F132">
         <v>5.5</v>
@@ -11975,7 +11975,7 @@
         <v>19</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="F133">
         <v>3</v>
@@ -12001,7 +12001,7 @@
         <v>25</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="F134">
         <v>5</v>
@@ -12027,7 +12027,7 @@
         <v>26</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="F135">
         <v>2</v>
@@ -12044,7 +12044,7 @@
         <v>135</v>
       </c>
       <c r="B136" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C136" s="1">
         <v>2</v>
@@ -12053,7 +12053,7 @@
         <v>20</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="F136">
         <v>5</v>
@@ -12070,7 +12070,7 @@
         <v>136</v>
       </c>
       <c r="B137" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C137" s="1">
         <v>2</v>
@@ -12079,7 +12079,7 @@
         <v>25</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="F137">
         <v>2</v>
@@ -12105,7 +12105,7 @@
         <v>18</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="F138">
         <v>6.5</v>
@@ -12122,7 +12122,7 @@
         <v>138</v>
       </c>
       <c r="B139" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C139" s="1">
         <v>1</v>
@@ -12131,7 +12131,7 @@
         <v>30</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="F139">
         <v>6.5</v>
@@ -12148,7 +12148,7 @@
         <v>139</v>
       </c>
       <c r="B140" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C140" s="1">
         <v>2</v>
@@ -12157,7 +12157,7 @@
         <v>24</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F140">
         <v>8</v>
@@ -12174,7 +12174,7 @@
         <v>140</v>
       </c>
       <c r="B141" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C141" s="1">
         <v>2</v>
@@ -12183,7 +12183,7 @@
         <v>34</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="F141">
         <v>5</v>
@@ -12209,7 +12209,7 @@
         <v>33</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="F142">
         <v>2</v>
@@ -12226,7 +12226,7 @@
         <v>142</v>
       </c>
       <c r="B143" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C143" s="1">
         <v>2</v>
@@ -12235,7 +12235,7 @@
         <v>19</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="F143">
         <v>6</v>
@@ -12252,7 +12252,7 @@
         <v>143</v>
       </c>
       <c r="B144" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C144" s="1">
         <v>2</v>
@@ -12261,7 +12261,7 @@
         <v>21</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="F144">
         <v>5</v>
@@ -12278,7 +12278,7 @@
         <v>144</v>
       </c>
       <c r="B145" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C145" s="1">
         <v>2</v>
@@ -12287,7 +12287,7 @@
         <v>20</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="F145">
         <v>2</v>
@@ -12313,7 +12313,7 @@
         <v>19</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="F146">
         <v>7</v>
@@ -12330,7 +12330,7 @@
         <v>146</v>
       </c>
       <c r="B147" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C147" s="1">
         <v>2</v>
@@ -12339,7 +12339,7 @@
         <v>19</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="F147">
         <v>5</v>
@@ -12356,7 +12356,7 @@
         <v>147</v>
       </c>
       <c r="B148" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C148" s="1">
         <v>1</v>
@@ -12365,7 +12365,7 @@
         <v>20</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="F148">
         <v>4.5</v>
@@ -12382,7 +12382,7 @@
         <v>148</v>
       </c>
       <c r="B149" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C149" s="1">
         <v>2</v>
@@ -12391,7 +12391,7 @@
         <v>20</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="F149">
         <v>5.5</v>
